--- a/TEST_CHECKLIST.xlsx
+++ b/TEST_CHECKLIST.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2013" uniqueCount="794">
   <si>
     <t>Metric</t>
   </si>
@@ -113,18 +113,21 @@
     <t>Auth</t>
   </si>
   <si>
-    <t>Phone OTP</t>
-  </si>
-  <si>
-    <t>Send OTP to new number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Go to /login
-2. Enter a valid Indian phone number never used before
-3. Click Send OTP</t>
-  </si>
-  <si>
-    <t>OTP is delivered on WhatsApp within ~30s; cooldown timer starts (60s)</t>
+    <t>Sign up — influencer</t>
+  </si>
+  <si>
+    <t>Happy path (no referral)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Visit /login as logged-out; pick Sign Up
+2. Step 1: choose role Influencer
+3. Step 2: complete Instagram Business Login OAuth (mandatory — cannot skip)
+4. Step 3: SignUpForm — name prefilled from IG where available; enter phone; Send OTP; enter code; Verify
+5. Step 4: pick categories (or Skip)
+6. Step 5: preferences (or Skip)</t>
+  </si>
+  <si>
+    <t>influencer_profiles row created (status=active, IG photo stored); 50 RC welcome bonus ledger row (locked 30d, expires 90d); welcome notification + email; landed on /influencer</t>
   </si>
   <si>
     <t>P0</t>
@@ -133,85 +136,249 @@
     <t>TC-0002</t>
   </si>
   <si>
-    <t>Rate limit — 60s cooldown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Send OTP to a valid number
-2. Immediately click Send OTP again</t>
-  </si>
-  <si>
-    <t>Second click is blocked; UI shows 'Please wait Xs before resending'</t>
+    <t>Happy path with referral (?ref=slug)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Visit /?ref=&lt;VALID_SLUG&gt; as logged-out (ref captured from URL)
+2. Complete the full signup flow: role → Instagram OAuth → form (phone + OTP) → categories → preferences</t>
+  </si>
+  <si>
+    <t>Everything from the no-referral case PLUS a referrals row in SIGNED_UP for the referrer; referrer gets 'a friend just signed up' notification + email</t>
   </si>
   <si>
     <t>TC-0003</t>
   </si>
   <si>
-    <t>Rate limit — 5/hr per phone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Send 5 OTPs to the same number back-to-back (respecting 60s cooldown)
-2. Try to send a 6th</t>
-  </si>
-  <si>
-    <t>6th attempt is refused; UI shows 'Too many attempts, try again later'</t>
+    <t>OTP embedded in form — resend at 60s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. On step 3, send OTP
+2. Observe the resend timer</t>
+  </si>
+  <si>
+    <t>Timer counts down from 1:00 (m:ss format, not 0:60 or 0:30); Resend enabled only at 0:00 — matches the backend's 60s cooldown</t>
+  </si>
+  <si>
+    <t>TC-0004</t>
+  </si>
+  <si>
+    <t>Sign up — brand</t>
+  </si>
+  <si>
+    <t>Happy path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Sign Up → role Brand
+2. Step 2: Instagram Connect (brands connect IG too)
+3. Step 3: BrandSignUpForm — brand details + GSTIN + phone + OTP verify
+4. Submit</t>
+  </si>
+  <si>
+    <t>brand_profiles row created with verification_status='verified', source='direct_signup', GSTIN metadata columns filled; landed on /brands</t>
+  </si>
+  <si>
+    <t>TC-0005</t>
+  </si>
+  <si>
+    <t>GSTIN validation</t>
+  </si>
+  <si>
+    <t>1. On BrandSignUpForm enter an invalid GSTIN (wrong checksum/format)</t>
+  </si>
+  <si>
+    <t>Inline error; submit blocked until a valid GSTIN or the field's fallback path is satisfied</t>
   </si>
   <si>
     <t>P1</t>
   </si>
   <si>
-    <t>TC-0004</t>
-  </si>
-  <si>
-    <t>Rate limit — 20/hr per IP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. From one browser/IP, send OTPs to 20 different numbers
-2. Try to send a 21st from same browser</t>
-  </si>
-  <si>
-    <t>21st attempt is refused; UI surfaces an IP-level rate limit message</t>
-  </si>
-  <si>
-    <t>TC-0005</t>
-  </si>
-  <si>
-    <t>Verify OTP — happy path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Receive an OTP
-2. Enter it within the 5-minute window
-3. Click Verify</t>
-  </si>
-  <si>
-    <t>Session is created; user routed to signup step if new, else dashboard</t>
-  </si>
-  <si>
     <t>TC-0006</t>
   </si>
   <si>
-    <t>Verify OTP — wrong code</t>
-  </si>
-  <si>
-    <t>1. Enter an incorrect 6-digit OTP</t>
-  </si>
-  <si>
-    <t>Error message shown; user stays on OTP screen; no session created</t>
+    <t>Sign up</t>
+  </si>
+  <si>
+    <t>Phone already registered</t>
+  </si>
+  <si>
+    <t>1. Start influencer signup with a phone that already has an account</t>
+  </si>
+  <si>
+    <t>check-uniqueness blocks before OTP: 'This phone number is already registered. Please sign in instead.'</t>
   </si>
   <si>
     <t>TC-0007</t>
   </si>
   <si>
-    <t>Verify OTP — expired code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Wait &gt; 5 minutes after receiving OTP
-2. Enter the code</t>
-  </si>
-  <si>
-    <t>Error 'Code expired'; user must resend</t>
+    <t>Duplicate device fingerprint auto-flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. In the same browser, complete signup as user A with a ref slug
+2. Sign out; complete signup as user B with the same ref slug</t>
+  </si>
+  <si>
+    <t>User B's referral row lands as MANUAL_REVIEW with review_reason=duplicate_device_fp</t>
   </si>
   <si>
     <t>TC-0008</t>
+  </si>
+  <si>
+    <t>Referral to inactive referrer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Cancel referrer's subscription (via admin or Stripe)
+2. New user signs up with that slug</t>
+  </si>
+  <si>
+    <t>Referral is NOT attributed (referrer_not_subscribed); referee still gets the welcome bonus</t>
+  </si>
+  <si>
+    <t>TC-0009</t>
+  </si>
+  <si>
+    <t>Sign in</t>
+  </si>
+  <si>
+    <t>Happy path — influencer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Pick Sign In → role Influencer
+2. Enter registered phone → Send OTP
+3. Enter code on the VerifyOTP screen → Verify</t>
+  </si>
+  <si>
+    <t>Session created WITHOUT creating a new user (mode=signin); redirected to /influencer</t>
+  </si>
+  <si>
+    <t>TC-0010</t>
+  </si>
+  <si>
+    <t>Happy path — brand</t>
+  </si>
+  <si>
+    <t>1. Same as above with role Brand and a registered brand phone</t>
+  </si>
+  <si>
+    <t>Redirected to /brands</t>
+  </si>
+  <si>
+    <t>TC-0011</t>
+  </si>
+  <si>
+    <t>Unknown number nudge</t>
+  </si>
+  <si>
+    <t>1. Sign In → enter a phone that has no account</t>
+  </si>
+  <si>
+    <t>'You don't exist with us. Kindly sign up first.' shown BEFORE any OTP is sent; number recorded in leads table</t>
+  </si>
+  <si>
+    <t>TC-0012</t>
+  </si>
+  <si>
+    <t>Role mismatch</t>
+  </si>
+  <si>
+    <t>1. Sign In as Influencer using a phone registered as a Brand</t>
+  </si>
+  <si>
+    <t>'This number is registered as a Brand. Please switch role and try again.' — no OTP sent</t>
+  </si>
+  <si>
+    <t>TC-0013</t>
+  </si>
+  <si>
+    <t>Deactivated account reactivation</t>
+  </si>
+  <si>
+    <t>1. Sign in with OTP on a deactivated account</t>
+  </si>
+  <si>
+    <t>Reactivation confirm screen appears (not a hard error); confirming re-verifies the same OTP with reactivate=true and restores the account</t>
+  </si>
+  <si>
+    <t>TC-0014</t>
+  </si>
+  <si>
+    <t>Wrong OTP</t>
+  </si>
+  <si>
+    <t>1. Enter an incorrect 6-digit code</t>
+  </si>
+  <si>
+    <t>Error shown; user stays on the OTP screen; no session created</t>
+  </si>
+  <si>
+    <t>TC-0015</t>
+  </si>
+  <si>
+    <t>Expired OTP</t>
+  </si>
+  <si>
+    <t>1. Wait &gt; 5 minutes after receiving the code, then submit it</t>
+  </si>
+  <si>
+    <t>'Code expired' style error; user must resend</t>
+  </si>
+  <si>
+    <t>TC-0016</t>
+  </si>
+  <si>
+    <t>OTP resend</t>
+  </si>
+  <si>
+    <t>Resend timer is 60s everywhere</t>
+  </si>
+  <si>
+    <t>1. Check the resend countdown on: sign-in VerifyOTP, influencer SignUpForm, BrandSignUpForm (web); and the same three on Android</t>
+  </si>
+  <si>
+    <t>All count down from 1:00 in m:ss; Resend enabled only at 0:00</t>
+  </si>
+  <si>
+    <t>TC-0017</t>
+  </si>
+  <si>
+    <t>Resend failure surfaces the server message</t>
+  </si>
+  <si>
+    <t>1. Trigger a resend during the backend cooldown window (or after caps below)</t>
+  </si>
+  <si>
+    <t>The exact server message appears in the error banner — resend is NOT silently swallowed; on success a brief 'OTP sent successfully!' flash shows</t>
+  </si>
+  <si>
+    <t>TC-0018</t>
+  </si>
+  <si>
+    <t>OTP rate limits</t>
+  </si>
+  <si>
+    <t>5/hr per phone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Send 5 OTPs to the same number (respecting the 60s cooldown)
+2. Attempt a 6th</t>
+  </si>
+  <si>
+    <t>Refused with 'Too many OTP requests for this number. Try again in an hour.' visible in the UI on both first-send and resend</t>
+  </si>
+  <si>
+    <t>TC-0019</t>
+  </si>
+  <si>
+    <t>20/hr per IP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. From one network, send OTPs to 20 different numbers
+2. Attempt a 21st</t>
+  </si>
+  <si>
+    <t>Refused with 'Too many OTP requests from your network. Try again in an hour.' visible in the UI</t>
+  </si>
+  <si>
+    <t>TC-0020</t>
   </si>
   <si>
     <t>Sessions</t>
@@ -227,7 +394,7 @@
     <t>Both sessions remain valid — first session is not invalidated (stable session_password)</t>
   </si>
   <si>
-    <t>TC-0009</t>
+    <t>TC-0021</t>
   </si>
   <si>
     <t>Admin+user cookie collision</t>
@@ -238,133 +405,66 @@
 3. Reload the influencer tab</t>
   </si>
   <si>
-    <t>Known issue until the cookie-name fix ships: influencer tab loses session. Any inline getUser check (escrow-fund) returns 401. Confirm the fail-early alert appears on 'Approve &amp; Pay'.</t>
-  </si>
-  <si>
-    <t>TC-0010</t>
-  </si>
-  <si>
-    <t>Session expiry on click</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Sign in, then let the tab sit unopened for &gt; 1 hour
-2. Return and click Approve &amp; Pay on a campaign application</t>
-  </si>
-  <si>
-    <t>Client shows 'Your session expired. Please sign in again and retry.' No 401 dumps to console</t>
-  </si>
-  <si>
-    <t>TC-0011</t>
-  </si>
-  <si>
-    <t>Signup</t>
-  </si>
-  <si>
-    <t>Influencer signup — happy path (with ref)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Visit /?ref=&lt;VALID_SLUG&gt; as a logged-out user
-2. Complete OTP
-3. Complete Instagram OAuth
-4. Fill full_name; submit</t>
-  </si>
-  <si>
-    <t>Profile created; 50 RC welcome bonus row in ledger (locked 30d); referral row in SIGNED_UP; welcome notification + email sent</t>
-  </si>
-  <si>
-    <t>TC-0012</t>
-  </si>
-  <si>
-    <t>Influencer signup — no referral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Visit /login (no ?ref query)
-2. Complete OTP + Instagram OAuth + name</t>
-  </si>
-  <si>
-    <t>Profile created; welcome bonus row present; NO referrals row created</t>
-  </si>
-  <si>
-    <t>TC-0013</t>
-  </si>
-  <si>
-    <t>Self-referral rejection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Get the current user's referral slug
-2. Sign out; sign up a NEW user with ?ref=&lt;own slug&gt; would be impossible — instead try to attribute their own slug via URL manipulation</t>
-  </si>
-  <si>
-    <t>attribute-referral rejects self_referral; no row is created</t>
-  </si>
-  <si>
-    <t>TC-0014</t>
-  </si>
-  <si>
-    <t>Referral to inactive referrer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Cancel referrer's subscription (via admin or Stripe)
-2. New user signs up with that slug</t>
-  </si>
-  <si>
-    <t>Referral is NOT attributed (referrer_not_subscribed reason); referee still keeps welcome bonus</t>
-  </si>
-  <si>
-    <t>TC-0015</t>
-  </si>
-  <si>
-    <t>Duplicate device fingerprint auto-flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. In the same browser, complete signup as user A with a ref slug
-2. Sign out, complete signup as user B with the same ref slug</t>
-  </si>
-  <si>
-    <t>User B's referral row lands as MANUAL_REVIEW with review_reason=duplicate_device_fp</t>
-  </si>
-  <si>
-    <t>TC-0016</t>
-  </si>
-  <si>
-    <t>Brand signup — happy path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Visit /login as logged-out
-2. OTP → select role 'Brand'
-3. Fill GSTIN + brand_name + email
-4. Submit</t>
-  </si>
-  <si>
-    <t>brand_profiles row created with verification_status='verified'; source='direct_signup'</t>
-  </si>
-  <si>
-    <t>TC-0017</t>
-  </si>
-  <si>
-    <t>Brand invitation flow</t>
+    <t>Known issue until the cookie-name fix ships: influencer tab loses session. Confirm the fail-early 'session expired' message appears on escrow actions instead of a raw 401.</t>
+  </si>
+  <si>
+    <t>TC-0022</t>
+  </si>
+  <si>
+    <t>Auth splash on /login reload</t>
+  </si>
+  <si>
+    <t>1. Reload /login while signed out</t>
+  </si>
+  <si>
+    <t>Pink circular loader shows briefly while AuthContext initialises, then the login UI renders (no infinite spinner)</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>TC-0023</t>
+  </si>
+  <si>
+    <t>Invitations</t>
+  </si>
+  <si>
+    <t>Brand invitation claim</t>
   </si>
   <si>
     <t xml:space="preserve">1. Admin creates a brand invitation with instagram handle X
-2. User signs up on same phone; provides handle X</t>
-  </si>
-  <si>
-    <t>Invitation is claimed (status='claimed', claimed_by set); campaigns from that invitation are re-parented to the new brand_id</t>
-  </si>
-  <si>
-    <t>TC-0018</t>
+2. User signs up as brand providing handle X</t>
+  </si>
+  <si>
+    <t>Invitation claimed (status='claimed', claimed_by set); campaigns created against the invitation re-parent to the new brand_id</t>
+  </si>
+  <si>
+    <t>TC-0024</t>
+  </si>
+  <si>
+    <t>Influencer invitation claim carries metadata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Admin invites an influencer with city/categories/creator_type set
+2. That person completes signup with the same IG handle</t>
+  </si>
+  <si>
+    <t>Invitation claimed; creator_type/categories/city from the invitation notes appear on the new influencer_profiles row</t>
+  </si>
+  <si>
+    <t>TC-0025</t>
   </si>
   <si>
     <t>Role mismatch on invitation</t>
   </si>
   <si>
-    <t>1. User invited as brand tries to sign up as influencer using same phone</t>
+    <t>1. User invited as brand tries to sign up as influencer using the same identity</t>
   </si>
   <si>
     <t>Role-mismatch interrupt shown with dedicated copy (not generic 'sign in instead')</t>
   </si>
   <si>
-    <t>TC-0019</t>
+    <t>TC-0026</t>
   </si>
   <si>
     <t>Subscriptions</t>
@@ -383,7 +483,7 @@
     <t>Prices refresh; monthly-equivalent shown under annual (₹75/mo etc.); Save 20% badge only on annual</t>
   </si>
   <si>
-    <t>TC-0020</t>
+    <t>TC-0027</t>
   </si>
   <si>
     <t>Current-plan pill</t>
@@ -395,7 +495,7 @@
     <t>Pro card shows Current Plan chip; upgrade CTAs only on Elite</t>
   </si>
   <si>
-    <t>TC-0021</t>
+    <t>TC-0028</t>
   </si>
   <si>
     <t>RC redemption toggle visibility</t>
@@ -408,7 +508,7 @@
     <t>First case: toggle hidden. Second case: toggle shows 'Apply my N RC at checkout (up to 50% off first invoice)'</t>
   </si>
   <si>
-    <t>TC-0022</t>
+    <t>TC-0029</t>
   </si>
   <si>
     <t>Stripe</t>
@@ -425,7 +525,7 @@
     <t>Verifying overlay for ≤12s; profile.subscription_plan flips; success modal shows subscription_id + payment_id</t>
   </si>
   <si>
-    <t>TC-0023</t>
+    <t>TC-0030</t>
   </si>
   <si>
     <t>Buy plan with RC applied</t>
@@ -440,7 +540,7 @@
     <t>First invoice discounted by the applied amount; REDEMPTION ledger row inserted by webhook with correct delta and note referencing sub id</t>
   </si>
   <si>
-    <t>TC-0024</t>
+    <t>TC-0031</t>
   </si>
   <si>
     <t>Referral qualifies + credits referrer</t>
@@ -453,7 +553,7 @@
     <t>referrals row flips to REWARDED with correct referrer_reward_rc; ledger has REFERRAL_EARN row; referrer receives 'You earned N RC' notification + email</t>
   </si>
   <si>
-    <t>TC-0025</t>
+    <t>TC-0032</t>
   </si>
   <si>
     <t>Referral hits daily cap → MANUAL_REVIEW</t>
@@ -466,7 +566,7 @@
     <t>B's referral row lands as MANUAL_REVIEW (not REWARDED); no credit to A; admin sees it under Manual review</t>
   </si>
   <si>
-    <t>TC-0026</t>
+    <t>TC-0033</t>
   </si>
   <si>
     <t>Clawback on refund within 7d</t>
@@ -479,7 +579,7 @@
     <t>Referral flips to REVERSED; negative CLAWBACK ledger row inserted; 'RC reclaimed' email + notification fire</t>
   </si>
   <si>
-    <t>TC-0027</t>
+    <t>TC-0034</t>
   </si>
   <si>
     <t>Clawback outside 7d — no-op</t>
@@ -492,10 +592,7 @@
     <t>Referral stays REWARDED; no CLAWBACK row inserted</t>
   </si>
   <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>TC-0028</t>
+    <t>TC-0035</t>
   </si>
   <si>
     <t>Razorpay</t>
@@ -509,7 +606,7 @@
     <t>Verifying overlay; profile.subscription_plan flips; success modal shows subscription_id</t>
   </si>
   <si>
-    <t>TC-0029</t>
+    <t>TC-0036</t>
   </si>
   <si>
     <t>Buy plan with RC applied (Offers-enabled account)</t>
@@ -524,7 +621,7 @@
     <t>First charge is discounted; REDEMPTION ledger row inserted from subscription.charged webhook with the applied amount</t>
   </si>
   <si>
-    <t>TC-0030</t>
+    <t>TC-0037</t>
   </si>
   <si>
     <t>RC toggle graceful fallback if Offers disabled</t>
@@ -536,7 +633,7 @@
     <t>Server-side create-offer fails silently; checkout still completes at full price; no REDEMPTION row inserted; log line records the fallback</t>
   </si>
   <si>
-    <t>TC-0031</t>
+    <t>TC-0038</t>
   </si>
   <si>
     <t>Cancel + downgrade</t>
@@ -552,7 +649,7 @@
     <t>profile.subscription_plan flips to starter; user retains RC balance</t>
   </si>
   <si>
-    <t>TC-0032</t>
+    <t>TC-0039</t>
   </si>
   <si>
     <t>Refer &amp; Earn</t>
@@ -570,7 +667,7 @@
     <t>Gate card shown: 'Subscribe to unlock referrals'; See plans button routes to /influencer/pricing</t>
   </si>
   <si>
-    <t>TC-0033</t>
+    <t>TC-0040</t>
   </si>
   <si>
     <t>Balance card — locked vs available</t>
@@ -584,7 +681,7 @@
     <t>Card shows Available (unlocked) prominently, with 'Locked +N RC' chip when applicable. Zero-RC user sees no ReferBalanceCard on the home tile.</t>
   </si>
   <si>
-    <t>TC-0034</t>
+    <t>TC-0041</t>
   </si>
   <si>
     <t>Share link copy</t>
@@ -596,7 +693,7 @@
     <t>Full URL rgossips.com/?ref=&lt;slug&gt; is copied to clipboard; 'Copied' feedback shows for ~1.6s</t>
   </si>
   <si>
-    <t>TC-0035</t>
+    <t>TC-0042</t>
   </si>
   <si>
     <t>Share on WhatsApp</t>
@@ -608,7 +705,7 @@
     <t>wa.me/?text=&lt;message with slug&gt; opens in a new tab</t>
   </si>
   <si>
-    <t>TC-0036</t>
+    <t>TC-0043</t>
   </si>
   <si>
     <t>Referrals list — statuses</t>
@@ -620,7 +717,7 @@
     <t>Statuses render with correct pill copy + colour: Pending, Signed up, Qualified, Rewarded, Reversed, Expired, Under review</t>
   </si>
   <si>
-    <t>TC-0037</t>
+    <t>TC-0044</t>
   </si>
   <si>
     <t>Ledger — welcome bonus row shows Locked chip</t>
@@ -632,7 +729,7 @@
     <t>Ledger row for WELCOME_BONUS shows an amber 'Locked' chip and 'unlocks &lt;date&gt;' subtext</t>
   </si>
   <si>
-    <t>TC-0038</t>
+    <t>TC-0045</t>
   </si>
   <si>
     <t>Redemption</t>
@@ -648,7 +745,7 @@
     <t>Only floor(299×0.5)=149 RC redeemed even though 1000 available; remaining 851 RC survives</t>
   </si>
   <si>
-    <t>TC-0039</t>
+    <t>TC-0046</t>
   </si>
   <si>
     <t>Locked RC cannot be spent</t>
@@ -661,7 +758,7 @@
     <t>Available RC = 0; toggle is hidden; if user calls redeem-rc directly it returns reason=no_balance</t>
   </si>
   <si>
-    <t>TC-0040</t>
+    <t>TC-0047</t>
   </si>
   <si>
     <t>Leaderboard</t>
@@ -677,7 +774,7 @@
     <t>Top referrers this month card shows up to 10 rows sorted by RC; 'You: #N' chip in header</t>
   </si>
   <si>
-    <t>TC-0041</t>
+    <t>TC-0048</t>
   </si>
   <si>
     <t>Self-hides when nobody qualified</t>
@@ -690,7 +787,7 @@
     <t>Leaderboard card is not rendered</t>
   </si>
   <si>
-    <t>TC-0042</t>
+    <t>TC-0049</t>
   </si>
   <si>
     <t>Home tile</t>
@@ -706,7 +803,7 @@
     <t>First case: tile visible on /influencer under Instagram banner; tap routes to /refer. Second case: tile absent.</t>
   </si>
   <si>
-    <t>TC-0043</t>
+    <t>TC-0050</t>
   </si>
   <si>
     <t>Mobile</t>
@@ -722,7 +819,7 @@
     <t>Gradient balance card shows 0 available + locked chip; ledger row for welcome bonus carries Locked chip</t>
   </si>
   <si>
-    <t>TC-0044</t>
+    <t>TC-0051</t>
   </si>
   <si>
     <t>Admin</t>
@@ -739,7 +836,7 @@
     <t>ADMIN_ADJUSTMENT row inserted with admin_id + 90d expires_at; balance increases; notification fires to user</t>
   </si>
   <si>
-    <t>TC-0045</t>
+    <t>TC-0052</t>
   </si>
   <si>
     <t>Manual RC deduct</t>
@@ -751,7 +848,7 @@
     <t>Row inserted with no expiry; balance drops; refuses if it would go negative; refuses if |delta| &gt; 10000</t>
   </si>
   <si>
-    <t>TC-0046</t>
+    <t>TC-0053</t>
   </si>
   <si>
     <t>Approve MANUAL_REVIEW</t>
@@ -764,7 +861,7 @@
     <t>Referral flips to REWARDED; REFERRAL_EARN row inserted; reviewed_at + reviewed_by stamped; referrer receives 'You earned N RC' notification + email</t>
   </si>
   <si>
-    <t>TC-0047</t>
+    <t>TC-0054</t>
   </si>
   <si>
     <t>Reject MANUAL_REVIEW</t>
@@ -776,7 +873,7 @@
     <t>Referral flips to REVERSED; reviewed_at + reviewed_by stamped; no ledger row inserted</t>
   </si>
   <si>
-    <t>TC-0048</t>
+    <t>TC-0055</t>
   </si>
   <si>
     <t>Analytics KPIs</t>
@@ -788,7 +885,7 @@
     <t>Top strip: Total/Rewarded/In-flight/Under review. Funnel strip: signup→rewarded %, clawback %, reversed, all-time signups. Cost strip: earned/welcome/admin/redeemed/clawback/outstanding.</t>
   </si>
   <si>
-    <t>TC-0049</t>
+    <t>TC-0056</t>
   </si>
   <si>
     <t>Trust Score</t>
@@ -807,7 +904,7 @@
     <t>Bands render as Elite / Trusted / Established / Emerging / Building Trust; no 'Poor' string anywhere</t>
   </si>
   <si>
-    <t>TC-0050</t>
+    <t>TC-0057</t>
   </si>
   <si>
     <t>Cold-start cap</t>
@@ -822,7 +919,7 @@
     <t>Displayed score is 720 exactly (cold-start clamp); tooltip explains the cap</t>
   </si>
   <si>
-    <t>TC-0051</t>
+    <t>TC-0058</t>
   </si>
   <si>
     <t>Score info modal</t>
@@ -837,7 +934,7 @@
     <t>Modal renders 'How Your Trust Score Works'; scale legend shows '300 · Building Trust' and '900 · Elite'; five pillars listed with weights (30/25/20/15/10)</t>
   </si>
   <si>
-    <t>TC-0052</t>
+    <t>TC-0059</t>
   </si>
   <si>
     <t>Colour map</t>
@@ -852,7 +949,7 @@
     <t>Pill colours per BAND_RING map: Elite=emerald, Trusted=blue, Established=indigo, Emerging=amber, Building Trust=slate</t>
   </si>
   <si>
-    <t>TC-0053</t>
+    <t>TC-0060</t>
   </si>
   <si>
     <t>Profile Type</t>
@@ -872,7 +969,7 @@
     <t>Invitation created with metadata.creator_type='meme_page'</t>
   </si>
   <si>
-    <t>TC-0054</t>
+    <t>TC-0061</t>
   </si>
   <si>
     <t>Admin edit</t>
@@ -887,7 +984,7 @@
     <t>influencer_profiles.creator_type updated; visible on subsequent edit form open</t>
   </si>
   <si>
-    <t>TC-0055</t>
+    <t>TC-0062</t>
   </si>
   <si>
     <t>Brand home cards</t>
@@ -902,7 +999,7 @@
     <t>Routes to /brands/search?profileType=meme_page; FilterDrawer shows Meme page chip selected; list filtered</t>
   </si>
   <si>
-    <t>TC-0056</t>
+    <t>TC-0063</t>
   </si>
   <si>
     <t>Filter Drawer</t>
@@ -917,7 +1014,7 @@
     <t>Section renders with two options: Meme page, Celebrity</t>
   </si>
   <si>
-    <t>TC-0057</t>
+    <t>TC-0064</t>
   </si>
   <si>
     <t>Campaigns</t>
@@ -937,19 +1034,69 @@
     <t>campaigns row created with status='active'; brand routed to detail page</t>
   </si>
   <si>
-    <t>TC-0058</t>
+    <t>TC-0065</t>
   </si>
   <si>
     <t>Save as draft</t>
   </si>
   <si>
-    <t>1. Fill title + required date fields; click Save Draft (no banner)</t>
-  </si>
-  <si>
-    <t>Row created with status='draft'; no banner required for drafts</t>
-  </si>
-  <si>
-    <t>TC-0059</t>
+    <t>1. Fill title + all required fields except banner; click Save Draft</t>
+  </si>
+  <si>
+    <t>Row created with status='draft'; banner is the only requirement drafts skip — dates/deliverables/categories/platforms are mandatory even for drafts (DB NOT NULL on dates)</t>
+  </si>
+  <si>
+    <t>TC-0066</t>
+  </si>
+  <si>
+    <t>Start date defaults to today</t>
+  </si>
+  <si>
+    <t>1. Open the New Campaign dialog</t>
+  </si>
+  <si>
+    <t>Start Date is prefilled with today's date (local timezone); Application Deadline and End Date stay empty</t>
+  </si>
+  <si>
+    <t>TC-0067</t>
+  </si>
+  <si>
+    <t>Validation order + focus</t>
+  </si>
+  <si>
+    <t>1. Leave everything empty; click Publish</t>
+  </si>
+  <si>
+    <t>Errors render inline under every failing field; the dialog scrolls to and FOCUSES the FIRST failing field in visual order (Title → Banner → Platforms → Deliverables → Categories → Schedule) — not the Schedule section first</t>
+  </si>
+  <si>
+    <t>TC-0068</t>
+  </si>
+  <si>
+    <t>Draft activation requires banner (styled popup)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Save a draft without a banner
+2. On the campaign detail, click the status button to activate it</t>
+  </si>
+  <si>
+    <t>Refused with the compact styled error popup (not a JS alert): 'Add a campaign banner before publishing…'. Draft stays draft. After uploading a banner via Edit, activation succeeds</t>
+  </si>
+  <si>
+    <t>TC-0069</t>
+  </si>
+  <si>
+    <t>Empty-description draft doesn't leak JSON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Create a draft leaving Description empty
+2. View the campaign card in /brands/campaigns and the detail page</t>
+  </si>
+  <si>
+    <t>No raw metadata JSON blob shown as the description; body renders empty. Pre-existing broken rows also display clean (reader-side healing)</t>
+  </si>
+  <si>
+    <t>TC-0070</t>
   </si>
   <si>
     <t>Auto budget-per-influencer</t>
@@ -961,7 +1108,7 @@
     <t>budget_per_influencer auto-fills to 2000; also updates when either input changes</t>
   </si>
   <si>
-    <t>TC-0060</t>
+    <t>TC-0071</t>
   </si>
   <si>
     <t>Tier auto-fills follower range</t>
@@ -973,7 +1120,7 @@
     <t>target_follower_min=10000, target_follower_max=100000</t>
   </si>
   <si>
-    <t>TC-0061</t>
+    <t>TC-0072</t>
   </si>
   <si>
     <t>Deadline vs end date validation</t>
@@ -985,7 +1132,7 @@
     <t>Error 'Application deadline must be on or before the campaign end date'</t>
   </si>
   <si>
-    <t>TC-0062</t>
+    <t>TC-0073</t>
   </si>
   <si>
     <t>Missing banner blocks publish</t>
@@ -994,10 +1141,52 @@
     <t>1. Try to publish without a banner</t>
   </si>
   <si>
-    <t>Error message; Publish disabled path prevents submit; Save Draft still works</t>
-  </si>
-  <si>
-    <t>TC-0063</t>
+    <t>Inline banner error + scroll/focus to the Banner section; Save Draft still works without one</t>
+  </si>
+  <si>
+    <t>TC-0074</t>
+  </si>
+  <si>
+    <t>Hinted fields align with neighbours</t>
+  </si>
+  <si>
+    <t>1. Open the dialog; compare a field with a hint (e.g. Description/Slots) against adjacent hint-less fields in the same row</t>
+  </si>
+  <si>
+    <t>Inputs sit flush at the same height — hints render BELOW the control, not between label and input</t>
+  </si>
+  <si>
+    <t>TC-0075</t>
+  </si>
+  <si>
+    <t>Match callout</t>
+  </si>
+  <si>
+    <t>Callout on every campaign detail</t>
+  </si>
+  <si>
+    <t>1. Open any campaign detail as the brand</t>
+  </si>
+  <si>
+    <t>Match banner always renders: 'N influencers match perfectly…' when N&gt;0 (includes pending admin invitations), or the softer 'No influencers currently match this brief' at 0. Click opens /brands/search with categories/cities/follower range prefilled</t>
+  </si>
+  <si>
+    <t>TC-0076</t>
+  </si>
+  <si>
+    <t>Match notify</t>
+  </si>
+  <si>
+    <t>Creators notified on publish</t>
+  </si>
+  <si>
+    <t>1. Publish a campaign whose criteria match at least one registered active creator</t>
+  </si>
+  <si>
+    <t>Matching registered creators receive a campaign_match notification; invitation-only matches count in the callout but get no notification</t>
+  </si>
+  <si>
+    <t>TC-0077</t>
   </si>
   <si>
     <t>Edit</t>
@@ -1012,7 +1201,7 @@
     <t>CreateCampaignDialog opens in edit mode with all fields prefilled; header is 'Edit Campaign'; footer is single 'Save Changes'</t>
   </si>
   <si>
-    <t>TC-0064</t>
+    <t>TC-0078</t>
   </si>
   <si>
     <t>Edit prefill includes images</t>
@@ -1024,7 +1213,7 @@
     <t>Existing banner shows with Replace + Trash overlay; gallery images render with X buttons</t>
   </si>
   <si>
-    <t>TC-0065</t>
+    <t>TC-0079</t>
   </si>
   <si>
     <t>Save Changes writes update</t>
@@ -1036,7 +1225,7 @@
     <t>brand-campaigns.update called; row updated; dialog closes; campaign detail refreshes with new title</t>
   </si>
   <si>
-    <t>TC-0066</t>
+    <t>TC-0080</t>
   </si>
   <si>
     <t>Status NOT touched on update</t>
@@ -1048,7 +1237,7 @@
     <t>Campaign stays paused; edit does not silently activate</t>
   </si>
   <si>
-    <t>TC-0067</t>
+    <t>TC-0081</t>
   </si>
   <si>
     <t>Not-editable modal when apps exist</t>
@@ -1060,7 +1249,7 @@
     <t>NotEditableModal opens with Pause and Duplicate as New buttons; count of applicants shown</t>
   </si>
   <si>
-    <t>TC-0068</t>
+    <t>TC-0082</t>
   </si>
   <si>
     <t>Server race guard on has_applications</t>
@@ -1075,7 +1264,7 @@
     <t>brand-campaigns.update returns has_applications; dialog closes; NotEditableModal opens</t>
   </si>
   <si>
-    <t>TC-0069</t>
+    <t>TC-0083</t>
   </si>
   <si>
     <t>Duplicate</t>
@@ -1090,7 +1279,7 @@
     <t>NotEditableModal closes; CreateCampaignDialog opens in create mode with source fields prefilled; title = 'Copy of &lt;original&gt;'; no server call yet</t>
   </si>
   <si>
-    <t>TC-0070</t>
+    <t>TC-0084</t>
   </si>
   <si>
     <t>Duplicate — cancel does not save</t>
@@ -1102,7 +1291,7 @@
     <t>Dialog closes; no new campaigns row inserted</t>
   </si>
   <si>
-    <t>TC-0071</t>
+    <t>TC-0085</t>
   </si>
   <si>
     <t>Duplicate — publish creates new row</t>
@@ -1114,7 +1303,7 @@
     <t>New campaigns row inserted (fresh id) with status='active'; brand routed to the new campaign detail</t>
   </si>
   <si>
-    <t>TC-0072</t>
+    <t>TC-0086</t>
   </si>
   <si>
     <t>Delete</t>
@@ -1130,7 +1319,7 @@
     <t>First: Delete button shows next to Edit. Second: Delete button hidden.</t>
   </si>
   <si>
-    <t>TC-0073</t>
+    <t>TC-0087</t>
   </si>
   <si>
     <t>Delete confirm + happy path</t>
@@ -1142,7 +1331,7 @@
     <t>Row hard-deleted; brand routed to /brands/campaigns; row no longer in list</t>
   </si>
   <si>
-    <t>TC-0074</t>
+    <t>TC-0088</t>
   </si>
   <si>
     <t>Delete race guard on has_applications</t>
@@ -1154,7 +1343,7 @@
     <t>Server returns has_applications; alert 'A creator applied to this campaign just now, so it cannot be deleted' shown; row remains</t>
   </si>
   <si>
-    <t>TC-0075</t>
+    <t>TC-0089</t>
   </si>
   <si>
     <t>Pause active campaign</t>
@@ -1166,7 +1355,7 @@
     <t>Status flips to paused; pill updates; no more applications visible on influencer side</t>
   </si>
   <si>
-    <t>TC-0076</t>
+    <t>TC-0090</t>
   </si>
   <si>
     <t>Resume paused campaign</t>
@@ -1178,7 +1367,7 @@
     <t>Status flips to active</t>
   </si>
   <si>
-    <t>TC-0077</t>
+    <t>TC-0091</t>
   </si>
   <si>
     <t>Discovery</t>
@@ -1194,7 +1383,7 @@
     <t>Only campaigns still accepting applications appear; those with passed deadlines are hidden unless the influencer applied</t>
   </si>
   <si>
-    <t>TC-0078</t>
+    <t>TC-0092</t>
   </si>
   <si>
     <t>Applied tab keeps deadline-passed campaigns</t>
@@ -1206,7 +1395,7 @@
     <t>Campaign still appears under Applied tab so the user can see status / submit deliverables</t>
   </si>
   <si>
-    <t>TC-0079</t>
+    <t>TC-0093</t>
   </si>
   <si>
     <t>Search + filter</t>
@@ -1219,7 +1408,7 @@
     <t>List filters live; empty state shown if no matches</t>
   </si>
   <si>
-    <t>TC-0080</t>
+    <t>TC-0094</t>
   </si>
   <si>
     <t>Application</t>
@@ -1235,7 +1424,7 @@
     <t>campaign_applications row created with status='pending'; campaign moves to Applied tab</t>
   </si>
   <si>
-    <t>TC-0081</t>
+    <t>TC-0095</t>
   </si>
   <si>
     <t>Cannot apply twice</t>
@@ -1247,133 +1436,253 @@
     <t>Button disabled; UI shows applied state instead</t>
   </si>
   <si>
-    <t>TC-0082</t>
+    <t>TC-0096</t>
+  </si>
+  <si>
+    <t>Negotiation</t>
+  </si>
+  <si>
+    <t>Send offer</t>
+  </si>
+  <si>
+    <t>Brand approves with price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. As brand, open a campaign with a pending application (compact card in the aside)
+2. Click the card → journey modal opens
+3. Click 'Approve with Price'; the creator's proposed rate seeds the input; adjust if desired
+4. Click Send Offer</t>
+  </si>
+  <si>
+    <t>Application flips to offer_sent with brand_offered_rate stored; NO money moves; influencer receives 'Offer: ₹N' notification; status history logs the offer with the amount</t>
+  </si>
+  <si>
+    <t>TC-0097</t>
+  </si>
+  <si>
+    <t>Offer requires a positive amount</t>
+  </si>
+  <si>
+    <t>1. In the offer form, clear the amount or enter 0; click Send Offer</t>
+  </si>
+  <si>
+    <t>Blocked with 'Enter an offer amount first'; server also rejects non-positive amounts</t>
+  </si>
+  <si>
+    <t>TC-0098</t>
+  </si>
+  <si>
+    <t>Offer only from pending</t>
+  </si>
+  <si>
+    <t>1. Attempt to send an offer on an application already in offer_sent (via devtools/API)</t>
+  </si>
+  <si>
+    <t>Server refuses: offer can only be sent on a pending application</t>
+  </si>
+  <si>
+    <t>TC-0099</t>
+  </si>
+  <si>
+    <t>Influencer response</t>
+  </si>
+  <si>
+    <t>Accept the offer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. As the influencer, open the campaign under Applied
+2. OfferResponseCard shows the offered amount (and 'you proposed X, brand countered' when they differ)
+3. Click Accept ₹N</t>
+  </si>
+  <si>
+    <t>Application flips to offer_accepted; brand receives 'Offer accepted — fund escrow' notification; influencer sees 'waiting for brand to fund escrow'</t>
+  </si>
+  <si>
+    <t>TC-0100</t>
+  </si>
+  <si>
+    <t>Withdraw instead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. On the OfferResponseCard click Withdraw
+2. Confirm in the inline 'Yes, Withdraw' step</t>
+  </si>
+  <si>
+    <t>Application flips to withdrawn; brand notified; campaign returns to the influencer's Active tab (re-apply possible); no counter-offer path exists anywhere</t>
+  </si>
+  <si>
+    <t>TC-0101</t>
+  </si>
+  <si>
+    <t>Influencer can only act on own application</t>
+  </si>
+  <si>
+    <t>1. POST update-application-status with influencerId of a different user (via API)</t>
+  </si>
+  <si>
+    <t>Server refuses: Not authorized</t>
+  </si>
+  <si>
+    <t>TC-0102</t>
   </si>
   <si>
     <t>Escrow</t>
   </si>
   <si>
-    <t>Approve + fund</t>
-  </si>
-  <si>
-    <t>Approve with agreed rate — happy path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. As brand, open campaign with pending application
-2. Set agreed rate; click Approve &amp; Pay
-3. Session check passes
-4. escrow-fund returns order_id + key_id
-5. Complete Razorpay Checkout with test card / UPI</t>
-  </si>
-  <si>
-    <t>campaign_applications row: status='approved', escrow_status='held', escrow_amount set (paise). Signature verified server-side.</t>
-  </si>
-  <si>
-    <t>TC-0083</t>
+    <t>Pay to escrow</t>
+  </si>
+  <si>
+    <t>Fund after acceptance — happy path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. As brand, open the accepted application (status chip 'Offer Accepted — Pay')
+2. Click 'Pay ₹N to Escrow' (amount is fixed — no input)
+3. Complete Razorpay Checkout with test card / UPI</t>
+  </si>
+  <si>
+    <t>status='approved', escrow_status='held', escrow_amount = accepted offer (paise), final_agreed_rate stamped from brand_offered_rate; creator gets the escrow-funded notification + email</t>
+  </si>
+  <si>
+    <t>TC-0103</t>
+  </si>
+  <si>
+    <t>Cannot fund before acceptance</t>
+  </si>
+  <si>
+    <t>1. Attempt escrow-fund on an application in pending or offer_sent (via API)</t>
+  </si>
+  <si>
+    <t>409: 'the creator must accept your offer before you fund escrow'</t>
+  </si>
+  <si>
+    <t>TC-0104</t>
+  </si>
+  <si>
+    <t>Amount tamper rejected</t>
+  </si>
+  <si>
+    <t>1. POST escrow-fund with an agreedRate different from the accepted offer</t>
+  </si>
+  <si>
+    <t>409: 'Amount mismatch: the accepted offer is ₹N.'</t>
+  </si>
+  <si>
+    <t>TC-0105</t>
   </si>
   <si>
     <t>Session expired — fail early</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Sign out (or clear cookies) leaving the campaign detail page open
-2. Click Approve &amp; Pay</t>
-  </si>
-  <si>
-    <t>Alert 'Your session expired. Please sign in again and retry.' No 401 popup; no Razorpay Checkout opened.</t>
-  </si>
-  <si>
-    <t>TC-0084</t>
-  </si>
-  <si>
-    <t>Idempotency — double-click Approve</t>
-  </si>
-  <si>
-    <t>1. Click Approve &amp; Pay very quickly twice</t>
-  </si>
-  <si>
-    <t>Only ONE Razorpay Order is created; second call returns already_held with the same order_id</t>
-  </si>
-  <si>
-    <t>TC-0085</t>
-  </si>
-  <si>
-    <t>Wrong brand — 403</t>
-  </si>
-  <si>
-    <t>1. Manually POST to escrow-fund with an application belonging to another brand</t>
-  </si>
-  <si>
-    <t>Server responds 403 forbidden; no order created</t>
-  </si>
-  <si>
-    <t>TC-0086</t>
+    <t>1. Clear cookies leaving the campaign detail open; click Pay to Escrow</t>
+  </si>
+  <si>
+    <t>Message 'Your session expired. Please sign in again and retry.' — no raw 401, no Razorpay Checkout opened</t>
+  </si>
+  <si>
+    <t>TC-0106</t>
+  </si>
+  <si>
+    <t>Idempotency — double-click</t>
+  </si>
+  <si>
+    <t>1. Click Pay to Escrow twice quickly</t>
+  </si>
+  <si>
+    <t>Only ONE Razorpay Order created; second call returns already_held with the same order_id</t>
+  </si>
+  <si>
+    <t>TC-0107</t>
+  </si>
+  <si>
+    <t>Journey</t>
+  </si>
+  <si>
+    <t>Compact cards + modal</t>
+  </si>
+  <si>
+    <t>Aside shows compact cards</t>
+  </si>
+  <si>
+    <t>1. Open a brand campaign with several applications</t>
+  </si>
+  <si>
+    <t>Right side lists compact cards only (DP + name + status pill); clicking one opens the journey modal</t>
+  </si>
+  <si>
+    <t>TC-0108</t>
+  </si>
+  <si>
+    <t>Timeline</t>
+  </si>
+  <si>
+    <t>Full history in the modal</t>
+  </si>
+  <si>
+    <t>1. Open the journey modal for an application that went applied → offer → accepted → funded → submitted → revision → resubmitted</t>
+  </si>
+  <si>
+    <t>Timeline lists every transition in order with timestamp, actor role (brand/influencer), and reasons (offer amount, revision note); current stage highlighted; the full review panel with stage actions renders below</t>
+  </si>
+  <si>
+    <t>TC-0109</t>
   </si>
   <si>
     <t>Content submission</t>
   </si>
   <si>
-    <t>Submit reel URL</t>
-  </si>
-  <si>
-    <t>1. As influencer with approved application, submit reel URL</t>
-  </si>
-  <si>
-    <t>status='submitted'; brand sees the URL in the application detail</t>
-  </si>
-  <si>
-    <t>TC-0087</t>
+    <t>Submit deliverables</t>
+  </si>
+  <si>
+    <t>1. As influencer with an approved (escrow-funded) application, submit draft links</t>
+  </si>
+  <si>
+    <t>status='submitted'; brand sees the links in the journey modal</t>
+  </si>
+  <si>
+    <t>TC-0110</t>
   </si>
   <si>
     <t>Brand requests revision</t>
   </si>
   <si>
-    <t>1. Brand clicks Request Revision, enters reason</t>
-  </si>
-  <si>
-    <t>status='revision_needed'; rejection_reason stored; influencer notified</t>
-  </si>
-  <si>
-    <t>TC-0088</t>
+    <t>1. In the journey modal, pick deliverables + note; Send for Revision</t>
+  </si>
+  <si>
+    <t>status='revision_needed'; reason + selected deliverables stored; influencer notified and sees the revision banner</t>
+  </si>
+  <si>
+    <t>TC-0111</t>
   </si>
   <si>
     <t>Live submission</t>
   </si>
   <si>
-    <t>Influencer marks live</t>
-  </si>
-  <si>
-    <t>1. After brand acceptance, influencer marks content live with URL</t>
-  </si>
-  <si>
-    <t>status='live_submitted'; metrics scraping begins</t>
-  </si>
-  <si>
-    <t>TC-0089</t>
+    <t>Influencer posts live</t>
+  </si>
+  <si>
+    <t>1. After drafts accepted, influencer submits live links</t>
+  </si>
+  <si>
+    <t>status='live_submitted'; metrics scraping kicks off</t>
+  </si>
+  <si>
+    <t>TC-0112</t>
   </si>
   <si>
     <t>Release</t>
   </si>
   <si>
-    <t>Accept &amp; Release Payment — happy path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Brand clicks Accept &amp; Release Payment (rate modal appears)
-2. Optionally rate influencer; confirm</t>
-  </si>
-  <si>
-    <t>escrow-release called with valid session; escrow_status='released'; influencer notified; entry added to payouts queue at /dashboard/payouts</t>
-  </si>
-  <si>
-    <t>TC-0090</t>
-  </si>
-  <si>
-    <t>1. Same session-expiry scenario as Approve</t>
-  </si>
-  <si>
-    <t>Alert shown; no release triggered</t>
-  </si>
-  <si>
-    <t>TC-0091</t>
+    <t>Accept &amp; Release Payment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Brand clicks Approve &amp; Release Payment (rating modal appears)
+2. Optionally rate; confirm</t>
+  </si>
+  <si>
+    <t>escrow-release runs with valid session; escrow_status released path; influencer notified; row appears in /dashboard/payouts queue</t>
+  </si>
+  <si>
+    <t>TC-0113</t>
   </si>
   <si>
     <t>Payouts (admin)</t>
@@ -1389,7 +1698,7 @@
     <t>Row updated; influencer notified with reference id</t>
   </si>
   <si>
-    <t>TC-0092</t>
+    <t>TC-0114</t>
   </si>
   <si>
     <t>Search</t>
@@ -1407,7 +1716,7 @@
     <t>List renders up to 50 InfluencerCards; 'Showing 50 of N creators' strip visible; Load More button shows remaining count</t>
   </si>
   <si>
-    <t>TC-0093</t>
+    <t>TC-0115</t>
   </si>
   <si>
     <t>Load More appends 50</t>
@@ -1419,7 +1728,7 @@
     <t>Next 50 rows appended below; counter updates; button disappears when total reached</t>
   </si>
   <si>
-    <t>TC-0094</t>
+    <t>TC-0116</t>
   </si>
   <si>
     <t>Server-side search</t>
@@ -1434,7 +1743,7 @@
     <t>Row appears in results (was previously invisible because of client-side truncation at 500)</t>
   </si>
   <si>
-    <t>TC-0095</t>
+    <t>TC-0117</t>
   </si>
   <si>
     <t>Filter — categories</t>
@@ -1449,7 +1758,7 @@
     <t>Only creators with that category (in influencer_profiles.categories[]) appear; total updates</t>
   </si>
   <si>
-    <t>TC-0096</t>
+    <t>TC-0118</t>
   </si>
   <si>
     <t>Filter — follower buckets</t>
@@ -1464,7 +1773,7 @@
     <t>Only creators with followers_count in [10000, 50000) appear</t>
   </si>
   <si>
-    <t>TC-0097</t>
+    <t>TC-0119</t>
   </si>
   <si>
     <t>Filter — profile type</t>
@@ -1479,7 +1788,7 @@
     <t>Only creators with creator_type='meme_page' appear</t>
   </si>
   <si>
-    <t>TC-0098</t>
+    <t>TC-0120</t>
   </si>
   <si>
     <t>Filter — locations</t>
@@ -1494,7 +1803,7 @@
     <t>Fuzzy substring match works both ways</t>
   </si>
   <si>
-    <t>TC-0099</t>
+    <t>TC-0121</t>
   </si>
   <si>
     <t>Sort</t>
@@ -1509,7 +1818,7 @@
     <t>Rows re-fetch from server with sort=alpha; results sorted A-Z on full_name || username</t>
   </si>
   <si>
-    <t>TC-0100</t>
+    <t>TC-0122</t>
   </si>
   <si>
     <t>Debounce</t>
@@ -1524,7 +1833,7 @@
     <t>Only 1-2 network requests fire, not 10 (300ms debounce)</t>
   </si>
   <si>
-    <t>TC-0101</t>
+    <t>TC-0123</t>
   </si>
   <si>
     <t>Stale-response guard</t>
@@ -1539,7 +1848,7 @@
     <t>Only the newest 'ab' results end up rendered; older responses discarded</t>
   </si>
   <si>
-    <t>TC-0102</t>
+    <t>TC-0124</t>
   </si>
   <si>
     <t>Photo fallback</t>
@@ -1555,7 +1864,7 @@
     <t>Card shows the custom photo, not the Instagram one</t>
   </si>
   <si>
-    <t>TC-0103</t>
+    <t>TC-0125</t>
   </si>
   <si>
     <t>Photos</t>
@@ -1574,7 +1883,7 @@
     <t>UserDoc + ProStatusCard show the custom photo (not the Instagram one)</t>
   </si>
   <si>
-    <t>TC-0104</t>
+    <t>TC-0126</t>
   </si>
   <si>
     <t>Campaign detail (brand side)</t>
@@ -1587,7 +1896,7 @@
     <t>Application row shows the custom photo — regression-fixed 2026-07 in brand-campaigns.get</t>
   </si>
   <si>
-    <t>TC-0105</t>
+    <t>TC-0127</t>
   </si>
   <si>
     <t>Upload</t>
@@ -1602,7 +1911,7 @@
     <t>Uploaded to storage; custom_profile_photo_url updated; avatar refreshes across surfaces</t>
   </si>
   <si>
-    <t>TC-0106</t>
+    <t>TC-0128</t>
   </si>
   <si>
     <t>Revert</t>
@@ -1617,7 +1926,7 @@
     <t>logo_url reset to the file uploaded at signup</t>
   </si>
   <si>
-    <t>TC-0107</t>
+    <t>TC-0129</t>
   </si>
   <si>
     <t>Instagram</t>
@@ -1635,7 +1944,7 @@
     <t>Access token stored; profile picture + basic stats populated</t>
   </si>
   <si>
-    <t>TC-0108</t>
+    <t>TC-0130</t>
   </si>
   <si>
     <t>Reconnect banner</t>
@@ -1648,7 +1957,7 @@
     <t>InstagramReconnectBanner appears; clicking Reconnect completes OAuth again</t>
   </si>
   <si>
-    <t>TC-0109</t>
+    <t>TC-0131</t>
   </si>
   <si>
     <t>Metrics</t>
@@ -1663,7 +1972,7 @@
     <t>reach value roughly ×28 vs a single day's number; if the token is fresh the request uses metric_type=time_series</t>
   </si>
   <si>
-    <t>TC-0110</t>
+    <t>TC-0132</t>
   </si>
   <si>
     <t>Gate check exposes boolean only</t>
@@ -1675,7 +1984,7 @@
     <t>Body contains 'instagram_connected: true|false'; never contains the raw access_token</t>
   </si>
   <si>
-    <t>TC-0111</t>
+    <t>TC-0133</t>
   </si>
   <si>
     <t>Notifications</t>
@@ -1694,7 +2003,7 @@
     <t>Count increments; opening the inbox marks the specific row read</t>
   </si>
   <si>
-    <t>TC-0112</t>
+    <t>TC-0134</t>
   </si>
   <si>
     <t>Referral email</t>
@@ -1709,7 +2018,7 @@
     <t>Referrer receives an email 'A friend joined RGossips with your link' via send-email</t>
   </si>
   <si>
-    <t>TC-0113</t>
+    <t>TC-0135</t>
   </si>
   <si>
     <t>EARN email fires</t>
@@ -1721,7 +2030,7 @@
     <t>Referrer receives 'You earned N RC' email + in-app row</t>
   </si>
   <si>
-    <t>TC-0114</t>
+    <t>TC-0136</t>
   </si>
   <si>
     <t>CLAWBACK email fires</t>
@@ -1733,7 +2042,7 @@
     <t>Referrer receives 'N RC reclaimed' email + in-app row</t>
   </si>
   <si>
-    <t>TC-0115</t>
+    <t>TC-0137</t>
   </si>
   <si>
     <t>Welcome email</t>
@@ -1748,7 +2057,7 @@
     <t>Welcome email delivered to that address</t>
   </si>
   <si>
-    <t>TC-0116</t>
+    <t>TC-0138</t>
   </si>
   <si>
     <t>Sidebar grouping</t>
@@ -1763,7 +2072,7 @@
     <t>Sidebar has Overview / Influencers / Brands / Operations / Admin Panel groups (last one only for super-admin)</t>
   </si>
   <si>
-    <t>TC-0117</t>
+    <t>TC-0139</t>
   </si>
   <si>
     <t>Users</t>
@@ -1779,7 +2088,7 @@
     <t>Their invitation row is deleted (not reset to pending); re-invite works cleanly (no 'you're already invited' loop)</t>
   </si>
   <si>
-    <t>TC-0118</t>
+    <t>TC-0140</t>
   </si>
   <si>
     <t>Featured Creators</t>
@@ -1794,7 +2103,7 @@
     <t>Row saved; order persists on refresh</t>
   </si>
   <si>
-    <t>TC-0119</t>
+    <t>TC-0141</t>
   </si>
   <si>
     <t>Featured Brands</t>
@@ -1806,7 +2115,7 @@
     <t>Same behaviour</t>
   </si>
   <si>
-    <t>TC-0120</t>
+    <t>TC-0142</t>
   </si>
   <si>
     <t>Featured Campaigns</t>
@@ -1815,7 +2124,7 @@
     <t>1. Same for Featured Campaigns</t>
   </si>
   <si>
-    <t>TC-0121</t>
+    <t>TC-0143</t>
   </si>
   <si>
     <t>Creator Stories</t>
@@ -1830,7 +2139,7 @@
     <t>Story published; visible on /brands landing carousel</t>
   </si>
   <si>
-    <t>TC-0122</t>
+    <t>TC-0144</t>
   </si>
   <si>
     <t>Disputes</t>
@@ -1845,7 +2154,7 @@
     <t>Row updated; both parties notified</t>
   </si>
   <si>
-    <t>TC-0123</t>
+    <t>TC-0145</t>
   </si>
   <si>
     <t>Services</t>
@@ -1860,7 +2169,7 @@
     <t>Service appears on /influencer/services</t>
   </si>
   <si>
-    <t>TC-0124</t>
+    <t>TC-0146</t>
   </si>
   <si>
     <t>Quote Requests</t>
@@ -1875,7 +2184,7 @@
     <t>Requester notified; row status updates</t>
   </si>
   <si>
-    <t>TC-0125</t>
+    <t>TC-0147</t>
   </si>
   <si>
     <t>Leads</t>
@@ -1890,7 +2199,7 @@
     <t>Details shown; phone + source visible</t>
   </si>
   <si>
-    <t>TC-0126</t>
+    <t>TC-0148</t>
   </si>
   <si>
     <t>Android</t>
@@ -1908,7 +2217,7 @@
     <t>Home screen loads; profile complete; welcome bonus visible on Refer screen (locked)</t>
   </si>
   <si>
-    <t>TC-0127</t>
+    <t>TC-0149</t>
   </si>
   <si>
     <t>Home</t>
@@ -1923,7 +2232,7 @@
     <t>Home shows ReferBalanceCard tile with Available + Locked; tap navigates to Refer screen</t>
   </si>
   <si>
-    <t>TC-0128</t>
+    <t>TC-0150</t>
   </si>
   <si>
     <t>Pricing</t>
@@ -1938,7 +2247,7 @@
     <t>Razorpay SDK opens; on payment the app polls profile and shows success; planId sent (was previously broken)</t>
   </si>
   <si>
-    <t>TC-0129</t>
+    <t>TC-0151</t>
   </si>
   <si>
     <t>RC toggle applies via Razorpay</t>
@@ -1950,7 +2259,7 @@
     <t>Offer created; discount applied on Razorpay screen; REDEMPTION posted via webhook</t>
   </si>
   <si>
-    <t>TC-0130</t>
+    <t>TC-0152</t>
   </si>
   <si>
     <t>Deep links</t>
@@ -1965,7 +2274,7 @@
     <t>App captures the ref param; signup path attributes referral on completion</t>
   </si>
   <si>
-    <t>TC-0131</t>
+    <t>TC-0153</t>
   </si>
   <si>
     <t>Refer screen</t>
@@ -1980,7 +2289,88 @@
     <t>Top referrers section renders with profile photos + RC values; 'You: #N' chip if applicable</t>
   </si>
   <si>
-    <t>TC-0132</t>
+    <t>TC-0154</t>
+  </si>
+  <si>
+    <t>Locations</t>
+  </si>
+  <si>
+    <t>Full city list + search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Filter Drawer → Location tab on /brands/search
+2. Type 'bang' in the search box</t>
+  </si>
+  <si>
+    <t>List holds ~600 Indian cities with 'Remote' pinned first; search narrows live; Bangalore AND Bengaluru both present</t>
+  </si>
+  <si>
+    <t>TC-0155</t>
+  </si>
+  <si>
+    <t>Influencer profile</t>
+  </si>
+  <si>
+    <t>Location multiselect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Influencer profile → My Information → tap the Location field
+2. Search + select 2 cities; Save Locations; save the profile</t>
+  </si>
+  <si>
+    <t>Chip modal with searchable city list; selections render as chips; stored as comma-joined text ('Mumbai, Pune'); brand-side Mumbai filter still finds this creator (fuzzy both ways)</t>
+  </si>
+  <si>
+    <t>TC-0156</t>
+  </si>
+  <si>
+    <t>Admin forms</t>
+  </si>
+  <si>
+    <t>City multiselect on invite + edit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Admin → Invite Influencer: City is a searchable multiselect (required)
+2. Admin → Edit Influencer + invited-row edit: same control, prefilled from stored value</t>
+  </si>
+  <si>
+    <t>Multi-city selection joins on save; legacy free-text like 'Mumbai, India' loads as just the recognised city chips</t>
+  </si>
+  <si>
+    <t>TC-0157</t>
+  </si>
+  <si>
+    <t>Landing</t>
+  </si>
+  <si>
+    <t>Footer</t>
+  </si>
+  <si>
+    <t>Pricing link is public</t>
+  </si>
+  <si>
+    <t>1. As a logged-out visitor, scroll to the footer and click Pricing</t>
+  </si>
+  <si>
+    <t>Lands on the home page scrolled to the #pricing section — NOT the auth-gated /influencer/pricing</t>
+  </si>
+  <si>
+    <t>TC-0158</t>
+  </si>
+  <si>
+    <t>How It Works</t>
+  </si>
+  <si>
+    <t>Compact 4-across layout</t>
+  </si>
+  <si>
+    <t>1. Scroll to How It Works on the landing page; toggle For Brands / For Influencers</t>
+  </si>
+  <si>
+    <t>Desktop shows the 4 steps as a single row of cards (no zigzag timeline with empty half-columns); toggle swaps content; mobile stacks slim cards</t>
+  </si>
+  <si>
+    <t>TC-0159</t>
   </si>
   <si>
     <t>A11y</t>
@@ -1989,17 +2379,32 @@
     <t>Dialogs</t>
   </si>
   <si>
-    <t>DialogTitle present on CreateCampaignDialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open Create/Edit dialog on desktop
+    <t>DialogTitle present on all dialogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the Create/Edit campaign dialog AND the Filter Drawer on desktop
 2. Inspect console</t>
   </si>
   <si>
-    <t>No Radix warning about missing DialogTitle</t>
-  </si>
-  <si>
-    <t>TC-0133</t>
+    <t>No Radix warning about missing DialogTitle / Description on either</t>
+  </si>
+  <si>
+    <t>TC-0160</t>
+  </si>
+  <si>
+    <t>Error popup</t>
+  </si>
+  <si>
+    <t>Compact styled error modal</t>
+  </si>
+  <si>
+    <t>1. Trigger a status-flip failure (e.g. activate a bannerless draft)</t>
+  </si>
+  <si>
+    <t>Compact modal (max-w-xs, small icon + 'Something went wrong' title, sm body, Close button) — never a raw window.alert</t>
+  </si>
+  <si>
+    <t>TC-0161</t>
   </si>
   <si>
     <t>Modals</t>
@@ -2014,7 +2419,7 @@
     <t>Modal closes; focus returns to trigger button</t>
   </si>
   <si>
-    <t>TC-0134</t>
+    <t>TC-0162</t>
   </si>
   <si>
     <t>Regression</t>
@@ -2031,7 +2436,7 @@
     <t>Both surfaces show the custom photo; no divergence</t>
   </si>
   <si>
-    <t>TC-0135</t>
+    <t>TC-0163</t>
   </si>
   <si>
     <t>list-influencers</t>
@@ -2046,7 +2451,7 @@
     <t>PocketFriendlyCreators carousel shows creators; not truncated to just 50 (uses limit:2000)</t>
   </si>
   <si>
-    <t>TC-0136</t>
+    <t>TC-0164</t>
   </si>
   <si>
     <t>list-campaigns</t>
@@ -2061,7 +2466,7 @@
     <t>Row absent from Active; if you had applied, it's still in Applied tab</t>
   </si>
   <si>
-    <t>TC-0137</t>
+    <t>TC-0165</t>
   </si>
   <si>
     <t>Trust score</t>
@@ -2522,7 +2927,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2530,7 +2935,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2538,7 +2943,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2546,7 +2951,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2554,7 +2959,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2621,7 +3026,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L138"/>
+  <dimension ref="A1:L166"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2770,8 +3175,8 @@
       <c r="F4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>46</v>
+      <c r="G4" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>7</v>
@@ -2791,13 +3196,13 @@
     </row>
     <row r="5" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>48</v>
@@ -2808,8 +3213,8 @@
       <c r="F5" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>46</v>
+      <c r="G5" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>7</v>
@@ -2835,7 +3240,7 @@
         <v>32</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>52</v>
@@ -2846,8 +3251,8 @@
       <c r="F6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>37</v>
+      <c r="G6" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>7</v>
@@ -2867,22 +3272,22 @@
     </row>
     <row r="7" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>37</v>
@@ -2905,25 +3310,25 @@
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>7</v>
@@ -2943,22 +3348,22 @@
     </row>
     <row r="9" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>37</v>
@@ -2981,22 +3386,22 @@
     </row>
     <row r="10" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>37</v>
@@ -3019,25 +3424,25 @@
     </row>
     <row r="11" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>46</v>
+        <v>77</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>7</v>
@@ -3057,22 +3462,22 @@
     </row>
     <row r="12" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>37</v>
@@ -3095,22 +3500,22 @@
     </row>
     <row r="13" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>37</v>
@@ -3133,25 +3538,25 @@
     </row>
     <row r="14" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>7</v>
@@ -3171,22 +3576,22 @@
     </row>
     <row r="15" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>37</v>
@@ -3209,25 +3614,25 @@
     </row>
     <row r="16" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>7</v>
@@ -3247,22 +3652,22 @@
     </row>
     <row r="17" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>37</v>
@@ -3285,25 +3690,25 @@
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>46</v>
+        <v>106</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>7</v>
@@ -3323,25 +3728,25 @@
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>7</v>
@@ -3361,25 +3766,25 @@
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>7</v>
@@ -3399,25 +3804,25 @@
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>46</v>
+        <v>120</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>7</v>
@@ -3437,22 +3842,22 @@
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>37</v>
@@ -3475,25 +3880,25 @@
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>37</v>
+        <v>128</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>7</v>
@@ -3513,25 +3918,25 @@
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>37</v>
+        <v>134</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>7</v>
@@ -3551,25 +3956,25 @@
     </row>
     <row r="25" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>37</v>
+        <v>138</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>7</v>
@@ -3589,25 +3994,25 @@
     </row>
     <row r="26" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>7</v>
@@ -3627,25 +4032,25 @@
     </row>
     <row r="27" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>7</v>
@@ -3665,25 +4070,25 @@
     </row>
     <row r="28" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="C28" s="3" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>7</v>
@@ -3703,22 +4108,22 @@
     </row>
     <row r="29" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>37</v>
@@ -3741,22 +4146,22 @@
     </row>
     <row r="30" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>37</v>
@@ -3779,25 +4184,25 @@
     </row>
     <row r="31" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>46</v>
+        <v>165</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>7</v>
@@ -3817,25 +4222,25 @@
     </row>
     <row r="32" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>46</v>
+        <v>169</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>7</v>
@@ -3855,25 +4260,25 @@
     </row>
     <row r="33" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>37</v>
+        <v>173</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>7</v>
@@ -3893,25 +4298,25 @@
     </row>
     <row r="34" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>37</v>
+        <v>177</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>7</v>
@@ -3931,25 +4336,25 @@
     </row>
     <row r="35" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>46</v>
+        <v>181</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>7</v>
@@ -3969,25 +4374,25 @@
     </row>
     <row r="36" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>46</v>
+        <v>185</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>7</v>
@@ -4007,25 +4412,25 @@
     </row>
     <row r="37" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>46</v>
+        <v>189</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>7</v>
@@ -4045,25 +4450,25 @@
     </row>
     <row r="38" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>37</v>
+        <v>193</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>7</v>
@@ -4083,25 +4488,25 @@
     </row>
     <row r="39" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>37</v>
+        <v>198</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>7</v>
@@ -4121,22 +4526,22 @@
     </row>
     <row r="40" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>37</v>
@@ -4159,25 +4564,25 @@
     </row>
     <row r="41" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="D41" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>46</v>
+        <v>208</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>7</v>
@@ -4197,25 +4602,25 @@
     </row>
     <row r="42" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>148</v>
+        <v>212</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>7</v>
@@ -4235,25 +4640,25 @@
     </row>
     <row r="43" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>7</v>
@@ -4273,25 +4678,25 @@
     </row>
     <row r="44" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>7</v>
@@ -4311,13 +4716,13 @@
     </row>
     <row r="45" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>222</v>
@@ -4352,22 +4757,22 @@
         <v>225</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>46</v>
+        <v>229</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>7</v>
@@ -4387,22 +4792,22 @@
     </row>
     <row r="47" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>37</v>
@@ -4425,25 +4830,25 @@
     </row>
     <row r="48" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>7</v>
@@ -4463,25 +4868,25 @@
     </row>
     <row r="49" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>46</v>
+        <v>242</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>7</v>
@@ -4501,25 +4906,25 @@
     </row>
     <row r="50" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>242</v>
+        <v>200</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>37</v>
+        <v>247</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>7</v>
@@ -4539,25 +4944,25 @@
     </row>
     <row r="51" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>242</v>
+        <v>200</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>7</v>
@@ -4577,25 +4982,25 @@
     </row>
     <row r="52" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>242</v>
+        <v>200</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>46</v>
+        <v>257</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>7</v>
@@ -4615,13 +5020,13 @@
     </row>
     <row r="53" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>242</v>
+        <v>200</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>259</v>
@@ -4632,8 +5037,8 @@
       <c r="F53" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="G53" s="6" t="s">
-        <v>148</v>
+      <c r="G53" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>7</v>
@@ -4656,22 +5061,22 @@
         <v>262</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="E54" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="F54" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>46</v>
+      <c r="G54" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>7</v>
@@ -4691,25 +5096,25 @@
     </row>
     <row r="55" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C55" s="3" t="s">
+      <c r="F55" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>272</v>
-      </c>
       <c r="G55" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>7</v>
@@ -4729,25 +5134,25 @@
     </row>
     <row r="56" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F56" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>277</v>
-      </c>
       <c r="G56" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>7</v>
@@ -4767,25 +5172,25 @@
     </row>
     <row r="57" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C57" s="3" t="s">
+      <c r="F57" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>148</v>
+      <c r="G57" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>7</v>
@@ -4805,25 +5210,25 @@
     </row>
     <row r="58" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="F58" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>37</v>
+      <c r="G58" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>7</v>
@@ -4843,25 +5248,25 @@
     </row>
     <row r="59" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="F59" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>292</v>
-      </c>
       <c r="G59" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>7</v>
@@ -4881,25 +5286,25 @@
     </row>
     <row r="60" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="D60" s="3" t="s">
+      <c r="F60" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>296</v>
-      </c>
       <c r="G60" s="6" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>7</v>
@@ -4919,13 +5324,13 @@
     </row>
     <row r="61" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>285</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>298</v>
@@ -4936,8 +5341,8 @@
       <c r="F61" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="G61" s="6" t="s">
-        <v>148</v>
+      <c r="G61" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>7</v>
@@ -4960,22 +5365,22 @@
         <v>301</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>7</v>
@@ -4995,25 +5400,25 @@
     </row>
     <row r="63" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>7</v>
@@ -5033,25 +5438,25 @@
     </row>
     <row r="64" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>37</v>
+        <v>315</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>7</v>
@@ -5071,25 +5476,25 @@
     </row>
     <row r="65" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>46</v>
+        <v>321</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>7</v>
@@ -5109,25 +5514,25 @@
     </row>
     <row r="66" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>310</v>
-      </c>
       <c r="D66" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>37</v>
+        <v>325</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>7</v>
@@ -5147,25 +5552,25 @@
     </row>
     <row r="67" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>37</v>
+        <v>329</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>7</v>
@@ -5185,22 +5590,22 @@
     </row>
     <row r="68" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>37</v>
@@ -5223,25 +5628,25 @@
     </row>
     <row r="69" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="G69" s="5" t="s">
-        <v>46</v>
+        <v>337</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>7</v>
@@ -5261,22 +5666,22 @@
     </row>
     <row r="70" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G70" s="4" t="s">
         <v>37</v>
@@ -5299,25 +5704,25 @@
     </row>
     <row r="71" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>37</v>
+        <v>345</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>7</v>
@@ -5337,25 +5742,25 @@
     </row>
     <row r="72" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>37</v>
+        <v>349</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>7</v>
@@ -5375,25 +5780,25 @@
     </row>
     <row r="73" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>348</v>
+        <v>318</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>37</v>
+        <v>353</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>7</v>
@@ -5413,25 +5818,25 @@
     </row>
     <row r="74" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>348</v>
+        <v>318</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>37</v>
+        <v>357</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>7</v>
@@ -5451,25 +5856,25 @@
     </row>
     <row r="75" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>348</v>
+        <v>318</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="G75" s="5" t="s">
-        <v>46</v>
+        <v>361</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>7</v>
@@ -5489,22 +5894,22 @@
     </row>
     <row r="76" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>26</v>
+        <v>363</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="G76" s="4" t="s">
         <v>37</v>
@@ -5527,25 +5932,25 @@
     </row>
     <row r="77" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>26</v>
+        <v>368</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>7</v>
@@ -5565,22 +5970,22 @@
     </row>
     <row r="78" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="G78" s="4" t="s">
         <v>37</v>
@@ -5603,25 +6008,25 @@
     </row>
     <row r="79" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>369</v>
-      </c>
       <c r="D79" s="3" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>7</v>
@@ -5641,25 +6046,25 @@
     </row>
     <row r="80" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="G80" s="5" t="s">
-        <v>46</v>
+        <v>384</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>7</v>
@@ -5679,22 +6084,22 @@
     </row>
     <row r="81" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G81" s="4" t="s">
         <v>37</v>
@@ -5717,25 +6122,25 @@
     </row>
     <row r="82" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="G82" s="5" t="s">
-        <v>46</v>
+        <v>392</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>7</v>
@@ -5755,25 +6160,25 @@
     </row>
     <row r="83" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>391</v>
+        <v>317</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>37</v>
+        <v>396</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>7</v>
@@ -5793,22 +6198,22 @@
     </row>
     <row r="84" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>391</v>
+        <v>317</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="G84" s="4" t="s">
         <v>37</v>
@@ -5831,25 +6236,25 @@
     </row>
     <row r="85" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>391</v>
+        <v>317</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="G85" s="5" t="s">
-        <v>46</v>
+        <v>405</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>7</v>
@@ -5869,25 +6274,25 @@
     </row>
     <row r="86" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>391</v>
+        <v>317</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="G86" s="5" t="s">
-        <v>46</v>
+        <v>409</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>7</v>
@@ -5907,25 +6312,25 @@
     </row>
     <row r="87" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>391</v>
+        <v>317</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="G87" s="5" t="s">
-        <v>46</v>
+        <v>414</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>7</v>
@@ -5945,25 +6350,25 @@
     </row>
     <row r="88" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>391</v>
+        <v>317</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="G88" s="5" t="s">
-        <v>46</v>
+        <v>418</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>7</v>
@@ -5983,25 +6388,25 @@
     </row>
     <row r="89" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>391</v>
+        <v>317</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>7</v>
@@ -6021,13 +6426,13 @@
     </row>
     <row r="90" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>391</v>
+        <v>317</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>423</v>
+        <v>26</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>424</v>
@@ -6062,22 +6467,22 @@
         <v>427</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>391</v>
+        <v>317</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>423</v>
+        <v>26</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>397</v>
+        <v>428</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>37</v>
+        <v>430</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>7</v>
@@ -6097,25 +6502,25 @@
     </row>
     <row r="92" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>391</v>
+        <v>317</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="G92" s="5" t="s">
-        <v>46</v>
+        <v>435</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>7</v>
@@ -6135,25 +6540,25 @@
     </row>
     <row r="93" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>436</v>
+        <v>317</v>
       </c>
       <c r="C93" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D93" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="E93" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="E93" s="3" t="s">
+      <c r="F93" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="F93" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>37</v>
+      <c r="G93" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>7</v>
@@ -6173,25 +6578,25 @@
     </row>
     <row r="94" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D94" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="D94" s="3" t="s">
+      <c r="E94" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="E94" s="3" t="s">
+      <c r="F94" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>37</v>
+      <c r="G94" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>7</v>
@@ -6211,22 +6616,22 @@
     </row>
     <row r="95" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="C95" s="3" t="s">
+      <c r="D95" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="E95" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="E95" s="3" t="s">
+      <c r="F95" s="3" t="s">
         <v>448</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>449</v>
       </c>
       <c r="G95" s="4" t="s">
         <v>37</v>
@@ -6249,25 +6654,25 @@
     </row>
     <row r="96" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D96" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="B96" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="C96" s="3" t="s">
+      <c r="E96" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="F96" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>454</v>
-      </c>
       <c r="G96" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>7</v>
@@ -6287,25 +6692,25 @@
     </row>
     <row r="97" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="B97" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="C97" s="3" t="s">
+      <c r="D97" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="E97" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="E97" s="3" t="s">
+      <c r="F97" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="F97" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="G97" s="5" t="s">
-        <v>46</v>
+      <c r="G97" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H97" s="3" t="s">
         <v>7</v>
@@ -6325,25 +6730,25 @@
     </row>
     <row r="98" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D98" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="B98" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="C98" s="3" t="s">
+      <c r="E98" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="F98" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="E98" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>464</v>
-      </c>
       <c r="G98" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H98" s="3" t="s">
         <v>7</v>
@@ -6363,25 +6768,25 @@
     </row>
     <row r="99" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="E99" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="C99" s="3" t="s">
+      <c r="F99" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="D99" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>469</v>
-      </c>
       <c r="G99" s="6" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>7</v>
@@ -6401,25 +6806,25 @@
     </row>
     <row r="100" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="E100" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="B100" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="C100" s="3" t="s">
+      <c r="F100" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="G100" s="5" t="s">
-        <v>46</v>
+      <c r="G100" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>7</v>
@@ -6439,25 +6844,25 @@
     </row>
     <row r="101" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="F101" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="B101" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="G101" s="6" t="s">
-        <v>148</v>
+      <c r="G101" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>7</v>
@@ -6477,25 +6882,25 @@
     </row>
     <row r="102" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="G102" s="6" t="s">
-        <v>148</v>
+        <v>479</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>7</v>
@@ -6515,22 +6920,22 @@
     </row>
     <row r="103" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="F103" s="3" t="s">
         <v>485</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>489</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>37</v>
@@ -6553,22 +6958,22 @@
     </row>
     <row r="104" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="G104" s="4" t="s">
         <v>37</v>
@@ -6591,25 +6996,25 @@
     </row>
     <row r="105" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B105" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D105" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="E105" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="D105" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>498</v>
-      </c>
       <c r="F105" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="G105" s="4" t="s">
-        <v>37</v>
+        <v>493</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H105" s="3" t="s">
         <v>7</v>
@@ -6629,25 +7034,25 @@
     </row>
     <row r="106" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>501</v>
+        <v>482</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="G106" s="5" t="s">
-        <v>46</v>
+        <v>497</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H106" s="3" t="s">
         <v>7</v>
@@ -6667,25 +7072,25 @@
     </row>
     <row r="107" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>506</v>
+        <v>482</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="G107" s="6" t="s">
-        <v>148</v>
+        <v>501</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H107" s="3" t="s">
         <v>7</v>
@@ -6705,22 +7110,22 @@
     </row>
     <row r="108" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="G108" s="4" t="s">
         <v>37</v>
@@ -6743,22 +7148,22 @@
     </row>
     <row r="109" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="B109" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="E109" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="F109" s="3" t="s">
         <v>512</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="F109" s="3" t="s">
-        <v>519</v>
       </c>
       <c r="G109" s="4" t="s">
         <v>37</v>
@@ -6781,25 +7186,25 @@
     </row>
     <row r="110" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>511</v>
+        <v>481</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>7</v>
@@ -6819,25 +7224,25 @@
     </row>
     <row r="111" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>511</v>
+        <v>481</v>
       </c>
       <c r="C111" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="F111" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="D111" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>528</v>
-      </c>
       <c r="G111" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H111" s="3" t="s">
         <v>7</v>
@@ -6857,25 +7262,25 @@
     </row>
     <row r="112" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>530</v>
+        <v>481</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="G112" s="6" t="s">
-        <v>148</v>
+        <v>526</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>7</v>
@@ -6895,25 +7300,25 @@
     </row>
     <row r="113" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="B113" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="E113" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="C113" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>538</v>
-      </c>
       <c r="F113" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="G113" s="5" t="s">
-        <v>46</v>
+        <v>531</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H113" s="3" t="s">
         <v>7</v>
@@ -6933,25 +7338,25 @@
     </row>
     <row r="114" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>530</v>
+        <v>481</v>
       </c>
       <c r="C114" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="F114" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="D114" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>543</v>
-      </c>
       <c r="G114" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>7</v>
@@ -6971,25 +7376,25 @@
     </row>
     <row r="115" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="G115" s="5" t="s">
-        <v>46</v>
+        <v>542</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>7</v>
@@ -7009,25 +7414,25 @@
     </row>
     <row r="116" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="G116" s="6" t="s">
-        <v>148</v>
+        <v>546</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H116" s="3" t="s">
         <v>7</v>
@@ -7047,25 +7452,25 @@
     </row>
     <row r="117" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>221</v>
+        <v>538</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="G117" s="5" t="s">
-        <v>46</v>
+        <v>551</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>7</v>
@@ -7085,25 +7490,25 @@
     </row>
     <row r="118" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>221</v>
+        <v>538</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H118" s="3" t="s">
         <v>7</v>
@@ -7123,25 +7528,25 @@
     </row>
     <row r="119" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>221</v>
+        <v>538</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="G119" s="6" t="s">
-        <v>148</v>
+        <v>561</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H119" s="3" t="s">
         <v>7</v>
@@ -7161,25 +7566,25 @@
     </row>
     <row r="120" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>221</v>
+        <v>538</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="D120" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="E120" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="E120" s="3" t="s">
-        <v>570</v>
-      </c>
       <c r="F120" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="G120" s="6" t="s">
-        <v>148</v>
+        <v>566</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H120" s="3" t="s">
         <v>7</v>
@@ -7199,25 +7604,25 @@
     </row>
     <row r="121" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>221</v>
+        <v>538</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>571</v>
       </c>
       <c r="G121" s="6" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>7</v>
@@ -7237,25 +7642,25 @@
     </row>
     <row r="122" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="E122" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="B122" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C122" s="3" t="s">
+      <c r="F122" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="D122" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="F122" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="G122" s="6" t="s">
-        <v>148</v>
+      <c r="G122" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H122" s="3" t="s">
         <v>7</v>
@@ -7275,25 +7680,25 @@
     </row>
     <row r="123" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="E123" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="B123" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C123" s="3" t="s">
+      <c r="F123" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="D123" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="F123" s="3" t="s">
-        <v>584</v>
-      </c>
       <c r="G123" s="6" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="H123" s="3" t="s">
         <v>7</v>
@@ -7313,25 +7718,25 @@
     </row>
     <row r="124" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="E124" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="B124" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C124" s="3" t="s">
+      <c r="F124" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="D124" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="F124" s="3" t="s">
-        <v>589</v>
-      </c>
       <c r="G124" s="6" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="H124" s="3" t="s">
         <v>7</v>
@@ -7351,25 +7756,25 @@
     </row>
     <row r="125" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="E125" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="B125" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C125" s="3" t="s">
+      <c r="F125" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="D125" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="F125" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="G125" s="6" t="s">
-        <v>148</v>
+      <c r="G125" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H125" s="3" t="s">
         <v>7</v>
@@ -7389,25 +7794,25 @@
     </row>
     <row r="126" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="D126" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="B126" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C126" s="3" t="s">
+      <c r="E126" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="D126" s="3" t="s">
+      <c r="F126" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="E126" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="F126" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="G126" s="6" t="s">
-        <v>148</v>
+      <c r="G126" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H126" s="3" t="s">
         <v>7</v>
@@ -7427,22 +7832,22 @@
     </row>
     <row r="127" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="E127" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="F127" s="3" t="s">
         <v>601</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="E127" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="F127" s="3" t="s">
-        <v>605</v>
       </c>
       <c r="G127" s="4" t="s">
         <v>37</v>
@@ -7465,25 +7870,25 @@
     </row>
     <row r="128" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="F128" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="B128" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="D128" s="3" t="s">
-        <v>608</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="F128" s="3" t="s">
-        <v>610</v>
-      </c>
       <c r="G128" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H128" s="3" t="s">
         <v>7</v>
@@ -7503,25 +7908,25 @@
     </row>
     <row r="129" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="F129" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="B129" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="D129" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>614</v>
-      </c>
-      <c r="F129" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="G129" s="4" t="s">
-        <v>37</v>
+      <c r="G129" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="H129" s="3" t="s">
         <v>7</v>
@@ -7541,25 +7946,25 @@
     </row>
     <row r="130" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="E130" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="B130" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="D130" s="3" t="s">
+      <c r="F130" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="E130" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="F130" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="G130" s="5" t="s">
-        <v>46</v>
+      <c r="G130" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H130" s="3" t="s">
         <v>7</v>
@@ -7579,25 +7984,25 @@
     </row>
     <row r="131" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="E131" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="B131" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="C131" s="3" t="s">
+      <c r="F131" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="D131" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="E131" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="F131" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="G131" s="5" t="s">
-        <v>46</v>
+      <c r="G131" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="H131" s="3" t="s">
         <v>7</v>
@@ -7617,25 +8022,25 @@
     </row>
     <row r="132" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="E132" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="B132" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="C132" s="3" t="s">
+      <c r="F132" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="D132" s="3" t="s">
-        <v>627</v>
-      </c>
-      <c r="E132" s="3" t="s">
-        <v>628</v>
-      </c>
-      <c r="F132" s="3" t="s">
-        <v>629</v>
-      </c>
-      <c r="G132" s="6" t="s">
-        <v>148</v>
+      <c r="G132" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H132" s="3" t="s">
         <v>7</v>
@@ -7655,25 +8060,25 @@
     </row>
     <row r="133" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="F133" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="B133" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="C133" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="D133" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="E133" s="3" t="s">
-        <v>634</v>
-      </c>
-      <c r="F133" s="3" t="s">
-        <v>635</v>
-      </c>
       <c r="G133" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H133" s="3" t="s">
         <v>7</v>
@@ -7693,25 +8098,25 @@
     </row>
     <row r="134" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="F134" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="B134" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="C134" s="3" t="s">
-        <v>637</v>
-      </c>
-      <c r="D134" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="E134" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="F134" s="3" t="s">
-        <v>640</v>
-      </c>
       <c r="G134" s="6" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="H134" s="3" t="s">
         <v>7</v>
@@ -7731,25 +8136,25 @@
     </row>
     <row r="135" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="F135" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="B135" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="D135" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="E135" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="F135" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="G135" s="4" t="s">
-        <v>37</v>
+      <c r="G135" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H135" s="3" t="s">
         <v>7</v>
@@ -7769,25 +8174,25 @@
     </row>
     <row r="136" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G136" s="4" t="s">
-        <v>37</v>
+        <v>645</v>
+      </c>
+      <c r="G136" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H136" s="3" t="s">
         <v>7</v>
@@ -7807,25 +8212,25 @@
     </row>
     <row r="137" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>652</v>
+        <v>638</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>37</v>
+        <v>649</v>
+      </c>
+      <c r="G137" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="H137" s="3" t="s">
         <v>7</v>
@@ -7845,45 +8250,1109 @@
     </row>
     <row r="138" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="G138" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J138" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K138" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L138" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C139" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="B138" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="C138" s="3" t="s">
+      <c r="D139" s="3" t="s">
         <v>657</v>
       </c>
-      <c r="D138" s="3" t="s">
+      <c r="E139" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="E138" s="3" t="s">
+      <c r="F139" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="F138" s="3" t="s">
+      <c r="G139" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J139" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K139" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L139" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="G138" s="4" t="s">
+      <c r="B140" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="G140" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H140" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J140" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K140" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L140" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="G141" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H141" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I141" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J141" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K141" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L141" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="G142" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H142" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J142" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K142" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L142" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="G143" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H143" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I143" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J143" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K143" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L143" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="G144" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H144" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I144" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J144" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K144" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L144" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="G145" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H145" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I145" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J145" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K145" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L145" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="G146" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H146" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J146" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K146" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L146" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="G147" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H147" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I147" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J147" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K147" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L147" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="G148" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H148" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I148" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J148" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K148" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L148" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G149" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H138" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I138" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J138" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K138" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L138" s="3" t="s">
+      <c r="H149" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I149" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J149" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K149" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L149" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H150" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I150" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J150" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K150" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L150" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G151" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H151" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I151" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J151" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K151" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L151" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="G152" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H152" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I152" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J152" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K152" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L152" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="G153" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H153" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I153" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J153" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K153" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L153" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="G154" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H154" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I154" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J154" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K154" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L154" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="G155" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H155" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I155" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J155" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K155" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L155" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="G156" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H156" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I156" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J156" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K156" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L156" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="G157" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H157" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I157" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J157" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K157" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L157" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H158" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I158" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J158" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K158" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L158" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="G159" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H159" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I159" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J159" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K159" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L159" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="G160" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H160" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I160" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J160" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K160" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L160" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="G161" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H161" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I161" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J161" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K161" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L161" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="G162" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H162" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I162" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J162" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K162" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L162" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="G163" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H163" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I163" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J163" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K163" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L163" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="G164" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H164" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I164" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J164" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K164" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L164" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="G165" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H165" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I165" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J165" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K165" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L165" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="G166" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H166" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I166" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J166" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K166" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L166" s="3" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid status" error="Pick one of: Pass, Fail, Blocked, Skipped, N/A" sqref="H2:H138">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid status" error="Pick one of: Pass, Fail, Blocked, Skipped, N/A" sqref="H2:H166">
       <formula1>"Pass,Fail,Blocked,Skipped,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/TEST_CHECKLIST.xlsx
+++ b/TEST_CHECKLIST.xlsx
@@ -1,18 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F43EA7-36A7-4AC8-865B-9386A6C3C122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Summary" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Test Cases" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Test Cases" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$H$1:$H$166</definedName>
+  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2013" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2013" uniqueCount="795">
   <si>
     <t>Metric</t>
   </si>
@@ -119,7 +126,7 @@
     <t>Happy path (no referral)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Visit /login as logged-out; pick Sign Up
+    <t>1. Visit /login as logged-out; pick Sign Up
 2. Step 1: choose role Influencer
 3. Step 2: complete Instagram Business Login OAuth (mandatory — cannot skip)
 4. Step 3: SignUpForm — name prefilled from IG where available; enter phone; Send OTP; enter code; Verify
@@ -139,7 +146,7 @@
     <t>Happy path with referral (?ref=slug)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Visit /?ref=&lt;VALID_SLUG&gt; as logged-out (ref captured from URL)
+    <t>1. Visit /?ref=&lt;VALID_SLUG&gt; as logged-out (ref captured from URL)
 2. Complete the full signup flow: role → Instagram OAuth → form (phone + OTP) → categories → preferences</t>
   </si>
   <si>
@@ -152,7 +159,7 @@
     <t>OTP embedded in form — resend at 60s</t>
   </si>
   <si>
-    <t xml:space="preserve">1. On step 3, send OTP
+    <t>1. On step 3, send OTP
 2. Observe the resend timer</t>
   </si>
   <si>
@@ -168,7 +175,7 @@
     <t>Happy path</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Sign Up → role Brand
+    <t>1. Sign Up → role Brand
 2. Step 2: Instagram Connect (brands connect IG too)
 3. Step 3: BrandSignUpForm — brand details + GSTIN + phone + OTP verify
 4. Submit</t>
@@ -213,7 +220,7 @@
     <t>Duplicate device fingerprint auto-flag</t>
   </si>
   <si>
-    <t xml:space="preserve">1. In the same browser, complete signup as user A with a ref slug
+    <t>1. In the same browser, complete signup as user A with a ref slug
 2. Sign out; complete signup as user B with the same ref slug</t>
   </si>
   <si>
@@ -226,7 +233,7 @@
     <t>Referral to inactive referrer</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Cancel referrer's subscription (via admin or Stripe)
+    <t>1. Cancel referrer's subscription (via admin or Stripe)
 2. New user signs up with that slug</t>
   </si>
   <si>
@@ -242,7 +249,7 @@
     <t>Happy path — influencer</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Pick Sign In → role Influencer
+    <t>1. Pick Sign In → role Influencer
 2. Enter registered phone → Send OTP
 3. Enter code on the VerifyOTP screen → Verify</t>
   </si>
@@ -358,7 +365,7 @@
     <t>5/hr per phone</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Send 5 OTPs to the same number (respecting the 60s cooldown)
+    <t>1. Send 5 OTPs to the same number (respecting the 60s cooldown)
 2. Attempt a 6th</t>
   </si>
   <si>
@@ -371,7 +378,7 @@
     <t>20/hr per IP</t>
   </si>
   <si>
-    <t xml:space="preserve">1. From one network, send OTPs to 20 different numbers
+    <t>1. From one network, send OTPs to 20 different numbers
 2. Attempt a 21st</t>
   </si>
   <si>
@@ -387,7 +394,7 @@
     <t>Multi-device sign-in</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Sign in as an influencer on browser A
+    <t>1. Sign in as an influencer on browser A
 2. Sign in as the same user on browser B without signing out of A</t>
   </si>
   <si>
@@ -400,7 +407,7 @@
     <t>Admin+user cookie collision</t>
   </si>
   <si>
-    <t xml:space="preserve">1. In the same browser, sign into rgossips.com as an influencer
+    <t>1. In the same browser, sign into rgossips.com as an influencer
 2. Open /dashboard (admin) and sign in as admin
 3. Reload the influencer tab</t>
   </si>
@@ -432,7 +439,7 @@
     <t>Brand invitation claim</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Admin creates a brand invitation with instagram handle X
+    <t>1. Admin creates a brand invitation with instagram handle X
 2. User signs up as brand providing handle X</t>
   </si>
   <si>
@@ -445,7 +452,7 @@
     <t>Influencer invitation claim carries metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Admin invites an influencer with city/categories/creator_type set
+    <t>1. Admin invites an influencer with city/categories/creator_type set
 2. That person completes signup with the same IG handle</t>
   </si>
   <si>
@@ -476,7 +483,7 @@
     <t>Toggle monthly/annual</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Visit /influencer/pricing
+    <t>1. Visit /influencer/pricing
 2. Toggle between monthly and annual</t>
   </si>
   <si>
@@ -501,7 +508,7 @@
     <t>RC redemption toggle visibility</t>
   </si>
   <si>
-    <t xml:space="preserve">1. As a user with 0 RC available, visit /influencer/pricing
+    <t>1. As a user with 0 RC available, visit /influencer/pricing
 2. As a user with N &gt; 0 RC available, visit /influencer/pricing</t>
   </si>
   <si>
@@ -517,7 +524,7 @@
     <t>Buy plan without RC</t>
   </si>
   <si>
-    <t xml:space="preserve">1. On pricing page, click Upgrade → Stripe
+    <t>1. On pricing page, click Upgrade → Stripe
 2. Complete Checkout on Stripe (test card 4242…)
 3. Return to /influencer/pricing?success=1</t>
   </si>
@@ -531,7 +538,7 @@
     <t>Buy plan with RC applied</t>
   </si>
   <si>
-    <t xml:space="preserve">1. With N &gt; 0 RC available, toggle Apply RC on
+    <t>1. With N &gt; 0 RC available, toggle Apply RC on
 2. Click Upgrade → Stripe
 3. Verify Checkout page shows a coupon with amount_off = min(N, floor(price×0.5))
 4. Complete payment</t>
@@ -546,7 +553,7 @@
     <t>Referral qualifies + credits referrer</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Sign up user B with user A's referral slug
+    <t>1. Sign up user B with user A's referral slug
 2. User B completes Stripe subscription</t>
   </si>
   <si>
@@ -559,7 +566,7 @@
     <t>Referral hits daily cap → MANUAL_REVIEW</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Manually mark 5 prior referrals as REWARDED for user A in the last 24h
+    <t>1. Manually mark 5 prior referrals as REWARDED for user A in the last 24h
 2. New referee B subscribes</t>
   </si>
   <si>
@@ -572,7 +579,7 @@
     <t>Clawback on refund within 7d</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Have a REWARDED referral &lt;7d old
+    <t>1. Have a REWARDED referral &lt;7d old
 2. Refund the referee's subscription in Stripe (test mode)</t>
   </si>
   <si>
@@ -585,7 +592,7 @@
     <t>Clawback outside 7d — no-op</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Have a REWARDED referral &gt; 7d old
+    <t>1. Have a REWARDED referral &gt; 7d old
 2. Refund the referee's subscription</t>
   </si>
   <si>
@@ -598,7 +605,7 @@
     <t>Razorpay</t>
   </si>
   <si>
-    <t xml:space="preserve">1. On pricing page, click Upgrade → Razorpay
+    <t>1. On pricing page, click Upgrade → Razorpay
 2. Complete embedded Checkout with test card / UPI
 3. Return via handler URL</t>
   </si>
@@ -612,7 +619,7 @@
     <t>Buy plan with RC applied (Offers-enabled account)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. With N &gt; 0 RC and Offers enabled on the RZP account
+    <t>1. With N &gt; 0 RC and Offers enabled on the RZP account
 2. Toggle Apply RC; click Upgrade → Razorpay
 3. Verify Checkout shows the discount
 4. Complete payment</t>
@@ -642,7 +649,7 @@
     <t>Cancel from Stripe dashboard</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Cancel a Pro subscription via Stripe (test)
+    <t>1. Cancel a Pro subscription via Stripe (test)
 2. Wait for customer.subscription.deleted webhook</t>
   </si>
   <si>
@@ -673,7 +680,7 @@
     <t>Balance card — locked vs available</t>
   </si>
   <si>
-    <t xml:space="preserve">1. As a fresh user with only the 50 RC welcome bonus (still within 30d lock)
+    <t>1. As a fresh user with only the 50 RC welcome bonus (still within 30d lock)
 2. As a user with earned RC (unlocked) + welcome bonus (still locked)
 3. As a user with no RC at all</t>
   </si>
@@ -738,7 +745,7 @@
     <t>50%-of-plan cap enforcement</t>
   </si>
   <si>
-    <t xml:space="preserve">1. As a user with 1000 RC available, buy Pro monthly (₹299)
+    <t>1. As a user with 1000 RC available, buy Pro monthly (₹299)
 2. Toggle Apply RC on</t>
   </si>
   <si>
@@ -751,7 +758,7 @@
     <t>Locked RC cannot be spent</t>
   </si>
   <si>
-    <t xml:space="preserve">1. As a user whose entire balance is the locked welcome bonus (30d not yet elapsed)
+    <t>1. As a user whose entire balance is the locked welcome bonus (30d not yet elapsed)
 2. Attempt to toggle RC at checkout</t>
   </si>
   <si>
@@ -767,7 +774,7 @@
     <t>Renders top 10 + your rank</t>
   </si>
   <si>
-    <t xml:space="preserve">1. As a user with at least 1 REWARDED referral this IST month
+    <t>1. As a user with at least 1 REWARDED referral this IST month
 2. Visit /influencer/refer</t>
   </si>
   <si>
@@ -780,7 +787,7 @@
     <t>Self-hides when nobody qualified</t>
   </si>
   <si>
-    <t xml:space="preserve">1. On the 1st of a month, before any REWARDED events
+    <t>1. On the 1st of a month, before any REWARDED events
 2. Visit /influencer/refer</t>
   </si>
   <si>
@@ -796,7 +803,7 @@
     <t>ReferBalanceCard visibility</t>
   </si>
   <si>
-    <t xml:space="preserve">1. As a user with any RC (locked + available &gt; 0)
+    <t>1. As a user with any RC (locked + available &gt; 0)
 2. As a user with 0 RC</t>
   </si>
   <si>
@@ -812,7 +819,7 @@
     <t>Locked balance display on ReferScreen</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Sign in as fresh user in Android app
+    <t>1. Sign in as fresh user in Android app
 2. Tap Refer &amp; Earn from profile</t>
   </si>
   <si>
@@ -828,7 +835,7 @@
     <t>Manual RC grant</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Admin visits /dashboard/referrals
+    <t>1. Admin visits /dashboard/referrals
 2. Enter userId + positive delta + note
 3. Submit</t>
   </si>
@@ -854,7 +861,7 @@
     <t>Approve MANUAL_REVIEW</t>
   </si>
   <si>
-    <t xml:space="preserve">1. As admin, filter to Manual review
+    <t>1. As admin, filter to Manual review
 2. Click Approve on a row</t>
   </si>
   <si>
@@ -897,7 +904,7 @@
     <t>Bands render with new labels</t>
   </si>
   <si>
-    <t xml:space="preserve">1. As a brand at any score band
+    <t>1. As a brand at any score band
 2. Open /brands (BrandHero) and /brands/profile (TrustSection)</t>
   </si>
   <si>
@@ -961,7 +968,7 @@
     <t>Set creator_type on invite</t>
   </si>
   <si>
-    <t xml:space="preserve">1. In /dashboard/influencers, click Invite
+    <t>1. In /dashboard/influencers, click Invite
 2. Fill required fields; select Profile Type = Meme page
 3. Submit</t>
   </si>
@@ -1026,7 +1033,7 @@
     <t>Publish new campaign (paid)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. As a brand, click New Campaign on /brands/campaigns
+    <t>1. As a brand, click New Campaign on /brands/campaigns
 2. Fill title, categories, budget, dates, at least 1 deliverable, banner
 3. Click Publish</t>
   </si>
@@ -1076,7 +1083,7 @@
     <t>Draft activation requires banner (styled popup)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Save a draft without a banner
+    <t>1. Save a draft without a banner
 2. On the campaign detail, click the status button to activate it</t>
   </si>
   <si>
@@ -1089,7 +1096,7 @@
     <t>Empty-description draft doesn't leak JSON</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Create a draft leaving Description empty
+    <t>1. Create a draft leaving Description empty
 2. View the campaign card in /brands/campaigns and the detail page</t>
   </si>
   <si>
@@ -1255,7 +1262,7 @@
     <t>Server race guard on has_applications</t>
   </si>
   <si>
-    <t xml:space="preserve">1. In devtools, force the applications count to appear 0
+    <t>1. In devtools, force the applications count to appear 0
 2. Click Edit, dialog opens
 3. Meanwhile someone applies
 4. Click Save Changes</t>
@@ -1312,7 +1319,7 @@
     <t>Delete visible only when 0 apps</t>
   </si>
   <si>
-    <t xml:space="preserve">1. On a campaign with 0 applications
+    <t>1. On a campaign with 0 applications
 2. On a campaign with any application</t>
   </si>
   <si>
@@ -1376,7 +1383,7 @@
     <t>Active tab hides deadline-passed campaigns</t>
   </si>
   <si>
-    <t xml:space="preserve">1. As influencer, visit /influencer/campaigns
+    <t>1. As influencer, visit /influencer/campaigns
 2. Verify that campaigns with application_deadline &lt; now are NOT in Active</t>
   </si>
   <si>
@@ -1401,7 +1408,7 @@
     <t>Search + filter</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Enter a search term
+    <t>1. Enter a search term
 2. Add categories + budget filters</t>
   </si>
   <si>
@@ -1417,7 +1424,7 @@
     <t>Apply — happy path</t>
   </si>
   <si>
-    <t xml:space="preserve">1. As influencer, open a campaign; click Apply
+    <t>1. As influencer, open a campaign; click Apply
 2. Enter proposed rate; submit</t>
   </si>
   <si>
@@ -1448,7 +1455,7 @@
     <t>Brand approves with price</t>
   </si>
   <si>
-    <t xml:space="preserve">1. As brand, open a campaign with a pending application (compact card in the aside)
+    <t>1. As brand, open a campaign with a pending application (compact card in the aside)
 2. Click the card → journey modal opens
 3. Click 'Approve with Price'; the creator's proposed rate seeds the input; adjust if desired
 4. Click Send Offer</t>
@@ -1490,7 +1497,7 @@
     <t>Accept the offer</t>
   </si>
   <si>
-    <t xml:space="preserve">1. As the influencer, open the campaign under Applied
+    <t>1. As the influencer, open the campaign under Applied
 2. OfferResponseCard shows the offered amount (and 'you proposed X, brand countered' when they differ)
 3. Click Accept ₹N</t>
   </si>
@@ -1504,7 +1511,7 @@
     <t>Withdraw instead</t>
   </si>
   <si>
-    <t xml:space="preserve">1. On the OfferResponseCard click Withdraw
+    <t>1. On the OfferResponseCard click Withdraw
 2. Confirm in the inline 'Yes, Withdraw' step</t>
   </si>
   <si>
@@ -1535,7 +1542,7 @@
     <t>Fund after acceptance — happy path</t>
   </si>
   <si>
-    <t xml:space="preserve">1. As brand, open the accepted application (status chip 'Offer Accepted — Pay')
+    <t>1. As brand, open the accepted application (status chip 'Offer Accepted — Pay')
 2. Click 'Pay ₹N to Escrow' (amount is fixed — no input)
 3. Complete Razorpay Checkout with test card / UPI</t>
   </si>
@@ -1675,7 +1682,7 @@
     <t>Accept &amp; Release Payment</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Brand clicks Approve &amp; Release Payment (rating modal appears)
+    <t>1. Brand clicks Approve &amp; Release Payment (rating modal appears)
 2. Optionally rate; confirm</t>
   </si>
   <si>
@@ -1691,7 +1698,7 @@
     <t>Mark payout as paid</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Admin visits /dashboard/payouts
+    <t>1. Admin visits /dashboard/payouts
 2. Marks a queued row as Paid with reference number</t>
   </si>
   <si>
@@ -1857,7 +1864,7 @@
     <t>Custom photo prefers over Instagram</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Have an influencer upload a custom_profile_photo_url
+    <t>1. Have an influencer upload a custom_profile_photo_url
 2. Search for them</t>
   </si>
   <si>
@@ -1876,7 +1883,7 @@
     <t>Influencer home</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Set custom_profile_photo_url on the current user
+    <t>1. Set custom_profile_photo_url on the current user
 2. Reload /influencer</t>
   </si>
   <si>
@@ -1889,7 +1896,7 @@
     <t>Campaign detail (brand side)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Have an approved application from an influencer with a custom photo
+    <t>1. Have an approved application from an influencer with a custom photo
 2. Open the brand campaign detail</t>
   </si>
   <si>
@@ -1950,7 +1957,7 @@
     <t>Reconnect banner</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Manually expire (or null) instagram_access_token in DB
+    <t>1. Manually expire (or null) instagram_access_token in DB
 2. Load /influencer</t>
   </si>
   <si>
@@ -1996,7 +2003,7 @@
     <t>Unread count updates in real time</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Trigger a notification from admin side
+    <t>1. Trigger a notification from admin side
 2. As user, watch the notifications bell</t>
   </si>
   <si>
@@ -2081,7 +2088,7 @@
     <t>Delete user + reinvite</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Delete an influencer via admin
+    <t>1. Delete an influencer via admin
 2. Immediately re-invite them with the same handle</t>
   </si>
   <si>
@@ -2298,7 +2305,7 @@
     <t>Full city list + search</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open Filter Drawer → Location tab on /brands/search
+    <t>1. Open Filter Drawer → Location tab on /brands/search
 2. Type 'bang' in the search box</t>
   </si>
   <si>
@@ -2314,7 +2321,7 @@
     <t>Location multiselect</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Influencer profile → My Information → tap the Location field
+    <t>1. Influencer profile → My Information → tap the Location field
 2. Search + select 2 cities; Save Locations; save the profile</t>
   </si>
   <si>
@@ -2330,7 +2337,7 @@
     <t>City multiselect on invite + edit</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Admin → Invite Influencer: City is a searchable multiselect (required)
+    <t>1. Admin → Invite Influencer: City is a searchable multiselect (required)
 2. Admin → Edit Influencer + invited-row edit: same control, prefilled from stored value</t>
   </si>
   <si>
@@ -2382,7 +2389,7 @@
     <t>DialogTitle present on all dialogs</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open the Create/Edit campaign dialog AND the Filter Drawer on desktop
+    <t>1. Open the Create/Edit campaign dialog AND the Filter Drawer on desktop
 2. Inspect console</t>
   </si>
   <si>
@@ -2428,7 +2435,7 @@
     <t>Home + campaign detail avatars align</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Set custom_profile_photo_url
+    <t>1. Set custom_profile_photo_url
 2. Reload /influencer
 3. As a brand, open a campaign detail with an application from this user</t>
   </si>
@@ -2479,38 +2486,56 @@
   </si>
   <si>
     <t>No occurrences of the old band strings anywhere user-facing</t>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFC00000"/>
+      <sz val="11"/>
+      <color rgb="FFB07000"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFB07000"/>
+      <sz val="11"/>
+      <color rgb="FF1E5AA6"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF1E5AA6"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2537,6 +2562,11 @@
         <fgColor rgb="FFE9F5FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2547,10 +2577,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2568,8 +2599,15 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2906,9 +2944,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -3020,14 +3058,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:L166"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -3042,7 +3081,7 @@
     <col min="12" max="12" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>19</v>
       </c>
@@ -3080,29 +3119,29 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" s="3" customFormat="1" ht="120" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="I2" s="3" t="s">
@@ -3118,29 +3157,29 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:12" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="7" t="s">
         <v>7</v>
       </c>
       <c r="I3" s="3" t="s">
@@ -3156,29 +3195,29 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:12" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="7" t="s">
         <v>7</v>
       </c>
       <c r="I4" s="3" t="s">
@@ -3194,7 +3233,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>46</v>
       </c>
@@ -3232,7 +3271,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>51</v>
       </c>
@@ -3270,29 +3309,29 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="7" t="s">
         <v>7</v>
       </c>
       <c r="I7" s="3" t="s">
@@ -3308,7 +3347,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>61</v>
       </c>
@@ -3346,7 +3385,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>65</v>
       </c>
@@ -3384,30 +3423,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>7</v>
+      <c r="H10" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>7</v>
@@ -3422,30 +3461,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>7</v>
+      <c r="H11" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>7</v>
@@ -3460,30 +3499,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>7</v>
+      <c r="H12" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>7</v>
@@ -3498,30 +3537,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>7</v>
+      <c r="H13" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>7</v>
@@ -3536,30 +3575,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>7</v>
+      <c r="H14" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>7</v>
@@ -3574,30 +3613,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>7</v>
+      <c r="H15" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>7</v>
@@ -3612,30 +3651,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>7</v>
+      <c r="H16" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>7</v>
@@ -3650,30 +3689,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>7</v>
+      <c r="H17" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>7</v>
@@ -3688,30 +3727,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>7</v>
+      <c r="H18" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>7</v>
@@ -3726,30 +3765,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>7</v>
+      <c r="H19" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>7</v>
@@ -3764,30 +3803,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>7</v>
+      <c r="H20" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>7</v>
@@ -3802,30 +3841,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>7</v>
+      <c r="H21" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>7</v>
@@ -3840,30 +3879,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>7</v>
+      <c r="H22" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>7</v>
@@ -3878,30 +3917,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>7</v>
+      <c r="H23" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>7</v>
@@ -3916,7 +3955,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>130</v>
       </c>
@@ -3954,29 +3993,29 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+    <row r="25" spans="1:12" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="G25" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="H25" s="7" t="s">
         <v>7</v>
       </c>
       <c r="I25" s="3" t="s">
@@ -3992,29 +4031,29 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+    <row r="26" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="H26" s="7" t="s">
         <v>7</v>
       </c>
       <c r="I26" s="3" t="s">
@@ -4030,30 +4069,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+    <row r="27" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="G27" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>7</v>
+      <c r="H27" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>7</v>
@@ -4068,30 +4107,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+    <row r="28" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H28" s="3" t="s">
-        <v>7</v>
+      <c r="H28" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>7</v>
@@ -4106,30 +4145,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+    <row r="29" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>7</v>
+      <c r="H29" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>7</v>
@@ -4144,30 +4183,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+    <row r="30" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H30" s="3" t="s">
-        <v>7</v>
+      <c r="H30" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>7</v>
@@ -4182,7 +4221,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>162</v>
       </c>
@@ -4220,7 +4259,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>166</v>
       </c>
@@ -4258,7 +4297,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>170</v>
       </c>
@@ -4296,7 +4335,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>174</v>
       </c>
@@ -4334,7 +4373,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>178</v>
       </c>
@@ -4372,30 +4411,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+    <row r="36" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F36" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>7</v>
+      <c r="H36" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>7</v>
@@ -4410,7 +4449,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>186</v>
       </c>
@@ -4448,7 +4487,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>190</v>
       </c>
@@ -4486,30 +4525,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
+    <row r="39" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="F39" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="G39" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H39" s="3" t="s">
-        <v>7</v>
+      <c r="H39" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>7</v>
@@ -4524,7 +4563,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>199</v>
       </c>
@@ -4562,7 +4601,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>205</v>
       </c>
@@ -4600,7 +4639,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>209</v>
       </c>
@@ -4676,7 +4715,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>217</v>
       </c>
@@ -4714,7 +4753,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>221</v>
       </c>
@@ -4752,7 +4791,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>225</v>
       </c>
@@ -4790,7 +4829,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>230</v>
       </c>
@@ -4828,7 +4867,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>234</v>
       </c>
@@ -4866,7 +4905,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>239</v>
       </c>
@@ -4904,7 +4943,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>243</v>
       </c>
@@ -4942,7 +4981,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>248</v>
       </c>
@@ -4980,7 +5019,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>253</v>
       </c>
@@ -5018,7 +5057,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>258</v>
       </c>
@@ -5056,7 +5095,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>262</v>
       </c>
@@ -5094,7 +5133,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>266</v>
       </c>
@@ -5132,7 +5171,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>270</v>
       </c>
@@ -5170,30 +5209,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
+    <row r="57" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D57" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="E57" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="F57" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="G57" s="4" t="s">
+      <c r="G57" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>7</v>
+      <c r="H57" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>7</v>
@@ -5208,7 +5247,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>280</v>
       </c>
@@ -5246,30 +5285,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
+    <row r="59" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="E59" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="F59" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="G59" s="5" t="s">
+      <c r="G59" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>7</v>
+      <c r="H59" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>7</v>
@@ -5284,30 +5323,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
+    <row r="60" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="D60" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="E60" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="F60" s="3" t="s">
+      <c r="F60" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="G60" s="6" t="s">
+      <c r="G60" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>7</v>
+      <c r="H60" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>7</v>
@@ -5322,7 +5361,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>295</v>
       </c>
@@ -5360,30 +5399,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
+    <row r="62" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="E62" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="F62" s="3" t="s">
+      <c r="F62" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="G62" s="5" t="s">
+      <c r="G62" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>7</v>
+      <c r="H62" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>7</v>
@@ -5398,30 +5437,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
+    <row r="63" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D63" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="E63" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="F63" s="3" t="s">
+      <c r="F63" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="G63" s="5" t="s">
+      <c r="G63" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H63" s="3" t="s">
-        <v>7</v>
+      <c r="H63" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>7</v>
@@ -5436,30 +5475,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
+    <row r="64" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D64" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="E64" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="F64" s="3" t="s">
+      <c r="F64" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="G64" s="6" t="s">
+      <c r="G64" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="H64" s="3" t="s">
-        <v>7</v>
+      <c r="H64" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>7</v>
@@ -5474,30 +5513,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
+    <row r="65" spans="1:12" s="3" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="D65" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E65" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="F65" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="G65" s="4" t="s">
+      <c r="G65" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H65" s="3" t="s">
-        <v>7</v>
+      <c r="H65" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>7</v>
@@ -5512,30 +5551,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
+    <row r="66" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="D66" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="E66" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="F66" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="G66" s="5" t="s">
+      <c r="G66" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>7</v>
+      <c r="H66" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>7</v>
@@ -5550,30 +5589,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
+    <row r="67" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D67" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="E67" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="F67" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="G67" s="5" t="s">
+      <c r="G67" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H67" s="3" t="s">
-        <v>7</v>
+      <c r="H67" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>7</v>
@@ -5588,30 +5627,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
+    <row r="68" spans="1:12" s="3" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="E68" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="F68" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="G68" s="4" t="s">
+      <c r="G68" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H68" s="3" t="s">
-        <v>7</v>
+      <c r="H68" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>7</v>
@@ -5626,30 +5665,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
+    <row r="69" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D69" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="E69" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="F69" s="3" t="s">
+      <c r="F69" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="G69" s="4" t="s">
+      <c r="G69" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H69" s="3" t="s">
-        <v>7</v>
+      <c r="H69" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>7</v>
@@ -5664,30 +5703,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
+    <row r="70" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D70" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E70" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="F70" s="3" t="s">
+      <c r="F70" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="G70" s="4" t="s">
+      <c r="G70" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H70" s="3" t="s">
-        <v>7</v>
+      <c r="H70" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>7</v>
@@ -5702,30 +5741,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
+    <row r="71" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E71" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="F71" s="3" t="s">
+      <c r="F71" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="G71" s="6" t="s">
+      <c r="G71" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="H71" s="3" t="s">
-        <v>7</v>
+      <c r="H71" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>7</v>
@@ -5740,30 +5779,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
+    <row r="72" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="E72" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="F72" s="3" t="s">
+      <c r="F72" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="G72" s="6" t="s">
+      <c r="G72" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>7</v>
+      <c r="H72" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>7</v>
@@ -5778,30 +5817,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
+    <row r="73" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="E73" s="3" t="s">
+      <c r="E73" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="F73" s="3" t="s">
+      <c r="F73" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G73" s="5" t="s">
+      <c r="G73" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H73" s="3" t="s">
-        <v>7</v>
+      <c r="H73" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>7</v>
@@ -5816,30 +5855,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
+    <row r="74" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D74" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="E74" s="3" t="s">
+      <c r="E74" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="F74" s="3" t="s">
+      <c r="F74" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="G74" s="5" t="s">
+      <c r="G74" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H74" s="3" t="s">
-        <v>7</v>
+      <c r="H74" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>7</v>
@@ -5854,30 +5893,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
+    <row r="75" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D75" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="E75" s="3" t="s">
+      <c r="E75" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="F75" s="3" t="s">
+      <c r="F75" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="G75" s="6" t="s">
+      <c r="G75" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="H75" s="3" t="s">
-        <v>7</v>
+      <c r="H75" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>7</v>
@@ -5892,30 +5931,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
+    <row r="76" spans="1:12" s="3" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="D76" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="E76" s="3" t="s">
+      <c r="E76" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="F76" s="3" t="s">
+      <c r="F76" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="G76" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>7</v>
+      <c r="H76" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>7</v>
@@ -5930,30 +5969,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="77" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
+    <row r="77" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C77" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D77" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="E77" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="F77" s="3" t="s">
+      <c r="F77" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="G77" s="5" t="s">
+      <c r="G77" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H77" s="3" t="s">
-        <v>7</v>
+      <c r="H77" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>7</v>
@@ -5968,30 +6007,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="78" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
+    <row r="78" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C78" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="E78" s="3" t="s">
+      <c r="E78" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="F78" s="3" t="s">
+      <c r="F78" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="G78" s="4" t="s">
+      <c r="G78" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H78" s="3" t="s">
-        <v>7</v>
+      <c r="H78" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>7</v>
@@ -6006,30 +6045,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="79" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
+    <row r="79" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="E79" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="F79" s="3" t="s">
+      <c r="F79" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="G79" s="5" t="s">
+      <c r="G79" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H79" s="3" t="s">
-        <v>7</v>
+      <c r="H79" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>7</v>
@@ -6044,30 +6083,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
+    <row r="80" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C80" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="E80" s="3" t="s">
+      <c r="E80" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="F80" s="3" t="s">
+      <c r="F80" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="G80" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H80" s="3" t="s">
-        <v>7</v>
+      <c r="H80" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>7</v>
@@ -6082,30 +6121,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
+    <row r="81" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C81" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D81" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="E81" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="F81" s="3" t="s">
+      <c r="F81" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="G81" s="4" t="s">
+      <c r="G81" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>7</v>
+      <c r="H81" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>7</v>
@@ -6120,30 +6159,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="3" t="s">
+    <row r="82" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C82" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D82" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="E82" s="3" t="s">
+      <c r="E82" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="F82" s="3" t="s">
+      <c r="F82" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="G82" s="4" t="s">
+      <c r="G82" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H82" s="3" t="s">
-        <v>7</v>
+      <c r="H82" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>7</v>
@@ -6158,30 +6197,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
+    <row r="83" spans="1:12" s="3" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="E83" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="F83" s="3" t="s">
+      <c r="F83" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="G83" s="5" t="s">
+      <c r="G83" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>7</v>
+      <c r="H83" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>7</v>
@@ -6196,30 +6235,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="s">
+    <row r="84" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C84" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D84" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="E84" s="3" t="s">
+      <c r="E84" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="F84" s="3" t="s">
+      <c r="F84" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="G84" s="4" t="s">
+      <c r="G84" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H84" s="3" t="s">
-        <v>7</v>
+      <c r="H84" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>7</v>
@@ -6234,30 +6273,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="85" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
+    <row r="85" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C85" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D85" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="E85" s="3" t="s">
+      <c r="E85" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="F85" s="3" t="s">
+      <c r="F85" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="G85" s="4" t="s">
+      <c r="G85" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H85" s="3" t="s">
-        <v>7</v>
+      <c r="H85" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>7</v>
@@ -6272,30 +6311,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
+    <row r="86" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C86" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="D86" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="E86" s="3" t="s">
+      <c r="E86" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="F86" s="3" t="s">
+      <c r="F86" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="G86" s="4" t="s">
+      <c r="G86" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H86" s="3" t="s">
-        <v>7</v>
+      <c r="H86" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>7</v>
@@ -6310,30 +6349,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="87" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
+    <row r="87" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C87" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D87" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="E87" s="3" t="s">
+      <c r="E87" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="F87" s="3" t="s">
+      <c r="F87" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="G87" s="4" t="s">
+      <c r="G87" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H87" s="3" t="s">
-        <v>7</v>
+      <c r="H87" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>7</v>
@@ -6348,30 +6387,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
+    <row r="88" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B88" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C88" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="D88" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="E88" s="3" t="s">
+      <c r="E88" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="F88" s="3" t="s">
+      <c r="F88" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="G88" s="4" t="s">
+      <c r="G88" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H88" s="3" t="s">
-        <v>7</v>
+      <c r="H88" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>7</v>
@@ -6386,30 +6425,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="3" t="s">
+    <row r="89" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C89" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="D89" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="E89" s="3" t="s">
+      <c r="E89" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="F89" s="3" t="s">
+      <c r="F89" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="G89" s="5" t="s">
+      <c r="G89" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>7</v>
+      <c r="H89" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>7</v>
@@ -6424,30 +6463,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="3" t="s">
+    <row r="90" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="7" t="s">
         <v>423</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C90" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="D90" s="7" t="s">
         <v>424</v>
       </c>
-      <c r="E90" s="3" t="s">
+      <c r="E90" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="F90" s="3" t="s">
+      <c r="F90" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="G90" s="4" t="s">
+      <c r="G90" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H90" s="3" t="s">
-        <v>7</v>
+      <c r="H90" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>7</v>
@@ -6462,30 +6501,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="3" t="s">
+    <row r="91" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C91" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D91" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="E91" s="3" t="s">
+      <c r="E91" s="7" t="s">
         <v>429</v>
       </c>
-      <c r="F91" s="3" t="s">
+      <c r="F91" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="G91" s="5" t="s">
+      <c r="G91" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>7</v>
+      <c r="H91" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>7</v>
@@ -6500,30 +6539,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="92" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="3" t="s">
+    <row r="92" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C92" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="D92" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="E92" s="3" t="s">
+      <c r="E92" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="F92" s="3" t="s">
+      <c r="F92" s="7" t="s">
         <v>435</v>
       </c>
-      <c r="G92" s="4" t="s">
+      <c r="G92" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H92" s="3" t="s">
-        <v>7</v>
+      <c r="H92" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>7</v>
@@ -6538,30 +6577,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="3" t="s">
+    <row r="93" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C93" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="D93" s="7" t="s">
         <v>437</v>
       </c>
-      <c r="E93" s="3" t="s">
+      <c r="E93" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="F93" s="3" t="s">
+      <c r="F93" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="G93" s="5" t="s">
+      <c r="G93" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H93" s="3" t="s">
-        <v>7</v>
+      <c r="H93" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>7</v>
@@ -6576,30 +6615,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="3" t="s">
+    <row r="94" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C94" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="E94" s="3" t="s">
+      <c r="E94" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="F94" s="3" t="s">
+      <c r="F94" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="G94" s="5" t="s">
+      <c r="G94" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>7</v>
+      <c r="H94" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>7</v>
@@ -6614,30 +6653,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="3" t="s">
+    <row r="95" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C95" s="7" t="s">
         <v>445</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="D95" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="E95" s="3" t="s">
+      <c r="E95" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="F95" s="3" t="s">
+      <c r="F95" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="G95" s="4" t="s">
+      <c r="G95" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H95" s="3" t="s">
-        <v>7</v>
+      <c r="H95" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>7</v>
@@ -6652,30 +6691,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="3" t="s">
+    <row r="96" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="C96" s="7" t="s">
         <v>445</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="E96" s="3" t="s">
+      <c r="E96" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="F96" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="G96" s="5" t="s">
+      <c r="G96" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>7</v>
+      <c r="H96" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>7</v>
@@ -6690,30 +6729,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="3" t="s">
+    <row r="97" spans="1:12" s="3" customFormat="1" ht="90" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C97" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="D97" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="E97" s="3" t="s">
+      <c r="E97" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="F97" s="3" t="s">
+      <c r="F97" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="G97" s="4" t="s">
+      <c r="G97" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H97" s="3" t="s">
-        <v>7</v>
+      <c r="H97" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>7</v>
@@ -6728,30 +6767,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="3" t="s">
+    <row r="98" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C98" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="D98" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="E98" s="3" t="s">
+      <c r="E98" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="F98" s="3" t="s">
+      <c r="F98" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="G98" s="5" t="s">
+      <c r="G98" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H98" s="3" t="s">
-        <v>7</v>
+      <c r="H98" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>7</v>
@@ -6766,30 +6805,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="3" t="s">
+    <row r="99" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="C99" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="D99" s="3" t="s">
+      <c r="D99" s="7" t="s">
         <v>464</v>
       </c>
-      <c r="E99" s="3" t="s">
+      <c r="E99" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="F99" s="3" t="s">
+      <c r="F99" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="G99" s="6" t="s">
+      <c r="G99" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="H99" s="3" t="s">
-        <v>7</v>
+      <c r="H99" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>7</v>
@@ -6804,30 +6843,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="3" t="s">
+    <row r="100" spans="1:12" s="3" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="C100" s="7" t="s">
         <v>468</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D100" s="7" t="s">
         <v>469</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="E100" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="F100" s="3" t="s">
+      <c r="F100" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="G100" s="4" t="s">
+      <c r="G100" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>7</v>
+      <c r="H100" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>7</v>
@@ -6842,30 +6881,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="3" t="s">
+    <row r="101" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="C101" s="7" t="s">
         <v>468</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="E101" s="3" t="s">
+      <c r="E101" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="F101" s="3" t="s">
+      <c r="F101" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="G101" s="4" t="s">
+      <c r="G101" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>7</v>
+      <c r="H101" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>7</v>
@@ -6880,30 +6919,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="3" t="s">
+    <row r="102" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="7" t="s">
         <v>476</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="B102" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="C102" s="3" t="s">
+      <c r="C102" s="7" t="s">
         <v>468</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="D102" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="E102" s="3" t="s">
+      <c r="E102" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="F102" s="3" t="s">
+      <c r="F102" s="7" t="s">
         <v>479</v>
       </c>
-      <c r="G102" s="5" t="s">
+      <c r="G102" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H102" s="3" t="s">
-        <v>7</v>
+      <c r="H102" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>7</v>
@@ -6918,30 +6957,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="3" t="s">
+    <row r="103" spans="1:12" s="3" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="7" t="s">
         <v>480</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C103" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="D103" s="7" t="s">
         <v>483</v>
       </c>
-      <c r="E103" s="3" t="s">
+      <c r="E103" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="F103" s="3" t="s">
+      <c r="F103" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="G103" s="4" t="s">
+      <c r="G103" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H103" s="3" t="s">
-        <v>7</v>
+      <c r="H103" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>7</v>
@@ -6956,30 +6995,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="3" t="s">
+    <row r="104" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="7" t="s">
         <v>486</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B104" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="C104" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="D104" s="3" t="s">
+      <c r="D104" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="E104" s="3" t="s">
+      <c r="E104" s="7" t="s">
         <v>488</v>
       </c>
-      <c r="F104" s="3" t="s">
+      <c r="F104" s="7" t="s">
         <v>489</v>
       </c>
-      <c r="G104" s="4" t="s">
+      <c r="G104" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H104" s="3" t="s">
-        <v>7</v>
+      <c r="H104" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>7</v>
@@ -6994,30 +7033,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="3" t="s">
+    <row r="105" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="7" t="s">
         <v>490</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B105" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="C105" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="D105" s="3" t="s">
+      <c r="D105" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="E105" s="3" t="s">
+      <c r="E105" s="7" t="s">
         <v>492</v>
       </c>
-      <c r="F105" s="3" t="s">
+      <c r="F105" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="G105" s="5" t="s">
+      <c r="G105" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H105" s="3" t="s">
-        <v>7</v>
+      <c r="H105" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>7</v>
@@ -7032,30 +7071,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="3" t="s">
+    <row r="106" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="7" t="s">
         <v>494</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B106" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="C106" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="D106" s="3" t="s">
+      <c r="D106" s="7" t="s">
         <v>495</v>
       </c>
-      <c r="E106" s="3" t="s">
+      <c r="E106" s="7" t="s">
         <v>496</v>
       </c>
-      <c r="F106" s="3" t="s">
+      <c r="F106" s="7" t="s">
         <v>497</v>
       </c>
-      <c r="G106" s="4" t="s">
+      <c r="G106" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H106" s="3" t="s">
-        <v>7</v>
+      <c r="H106" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>7</v>
@@ -7070,30 +7109,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="3" t="s">
+    <row r="107" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="7" t="s">
         <v>498</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B107" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="C107" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="D107" s="3" t="s">
+      <c r="D107" s="7" t="s">
         <v>499</v>
       </c>
-      <c r="E107" s="3" t="s">
+      <c r="E107" s="7" t="s">
         <v>500</v>
       </c>
-      <c r="F107" s="3" t="s">
+      <c r="F107" s="7" t="s">
         <v>501</v>
       </c>
-      <c r="G107" s="5" t="s">
+      <c r="G107" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H107" s="3" t="s">
-        <v>7</v>
+      <c r="H107" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>7</v>
@@ -7108,30 +7147,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="3" t="s">
+    <row r="108" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="7" t="s">
         <v>502</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="B108" s="7" t="s">
         <v>503</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="C108" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="D108" s="3" t="s">
+      <c r="D108" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="E108" s="3" t="s">
+      <c r="E108" s="7" t="s">
         <v>506</v>
       </c>
-      <c r="F108" s="3" t="s">
+      <c r="F108" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="G108" s="4" t="s">
+      <c r="G108" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H108" s="3" t="s">
-        <v>7</v>
+      <c r="H108" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>7</v>
@@ -7146,30 +7185,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="3" t="s">
+    <row r="109" spans="1:12" s="3" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="7" t="s">
         <v>508</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B109" s="7" t="s">
         <v>503</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="C109" s="7" t="s">
         <v>509</v>
       </c>
-      <c r="D109" s="3" t="s">
+      <c r="D109" s="7" t="s">
         <v>510</v>
       </c>
-      <c r="E109" s="3" t="s">
+      <c r="E109" s="7" t="s">
         <v>511</v>
       </c>
-      <c r="F109" s="3" t="s">
+      <c r="F109" s="7" t="s">
         <v>512</v>
       </c>
-      <c r="G109" s="4" t="s">
+      <c r="G109" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H109" s="3" t="s">
-        <v>7</v>
+      <c r="H109" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>7</v>
@@ -7184,30 +7223,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="3" t="s">
+    <row r="110" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="7" t="s">
         <v>513</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="B110" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="C110" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="D110" s="3" t="s">
+      <c r="D110" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="E110" s="3" t="s">
+      <c r="E110" s="7" t="s">
         <v>516</v>
       </c>
-      <c r="F110" s="3" t="s">
+      <c r="F110" s="7" t="s">
         <v>517</v>
       </c>
-      <c r="G110" s="5" t="s">
+      <c r="G110" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H110" s="3" t="s">
-        <v>7</v>
+      <c r="H110" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>7</v>
@@ -7222,30 +7261,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="3" t="s">
+    <row r="111" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="7" t="s">
         <v>518</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B111" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="C111" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="D111" s="3" t="s">
+      <c r="D111" s="7" t="s">
         <v>519</v>
       </c>
-      <c r="E111" s="3" t="s">
+      <c r="E111" s="7" t="s">
         <v>520</v>
       </c>
-      <c r="F111" s="3" t="s">
+      <c r="F111" s="7" t="s">
         <v>521</v>
       </c>
-      <c r="G111" s="5" t="s">
+      <c r="G111" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H111" s="3" t="s">
-        <v>7</v>
+      <c r="H111" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>7</v>
@@ -7260,30 +7299,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="3" t="s">
+    <row r="112" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="7" t="s">
         <v>522</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="B112" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="C112" s="7" t="s">
         <v>523</v>
       </c>
-      <c r="D112" s="3" t="s">
+      <c r="D112" s="7" t="s">
         <v>524</v>
       </c>
-      <c r="E112" s="3" t="s">
+      <c r="E112" s="7" t="s">
         <v>525</v>
       </c>
-      <c r="F112" s="3" t="s">
+      <c r="F112" s="7" t="s">
         <v>526</v>
       </c>
-      <c r="G112" s="5" t="s">
+      <c r="G112" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H112" s="3" t="s">
-        <v>7</v>
+      <c r="H112" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>7</v>
@@ -7298,30 +7337,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="3" t="s">
+    <row r="113" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="7" t="s">
         <v>527</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="C113" s="7" t="s">
         <v>528</v>
       </c>
-      <c r="D113" s="3" t="s">
+      <c r="D113" s="7" t="s">
         <v>529</v>
       </c>
-      <c r="E113" s="3" t="s">
+      <c r="E113" s="7" t="s">
         <v>530</v>
       </c>
-      <c r="F113" s="3" t="s">
+      <c r="F113" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="G113" s="4" t="s">
+      <c r="G113" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H113" s="3" t="s">
-        <v>7</v>
+      <c r="H113" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>7</v>
@@ -7336,30 +7375,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="3" t="s">
+    <row r="114" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B114" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="C114" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="D114" s="3" t="s">
+      <c r="D114" s="7" t="s">
         <v>534</v>
       </c>
-      <c r="E114" s="3" t="s">
+      <c r="E114" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="F114" s="3" t="s">
+      <c r="F114" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="G114" s="5" t="s">
+      <c r="G114" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H114" s="3" t="s">
-        <v>7</v>
+      <c r="H114" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>7</v>
@@ -7374,30 +7413,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="3" t="s">
+    <row r="115" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B115" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="C115" s="7" t="s">
         <v>539</v>
       </c>
-      <c r="D115" s="3" t="s">
+      <c r="D115" s="7" t="s">
         <v>540</v>
       </c>
-      <c r="E115" s="3" t="s">
+      <c r="E115" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="F115" s="3" t="s">
+      <c r="F115" s="7" t="s">
         <v>542</v>
       </c>
-      <c r="G115" s="4" t="s">
+      <c r="G115" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H115" s="3" t="s">
-        <v>7</v>
+      <c r="H115" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>7</v>
@@ -7412,30 +7451,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="116" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="3" t="s">
+    <row r="116" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="7" t="s">
         <v>543</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="B116" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="C116" s="7" t="s">
         <v>539</v>
       </c>
-      <c r="D116" s="3" t="s">
+      <c r="D116" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="E116" s="3" t="s">
+      <c r="E116" s="7" t="s">
         <v>545</v>
       </c>
-      <c r="F116" s="3" t="s">
+      <c r="F116" s="7" t="s">
         <v>546</v>
       </c>
-      <c r="G116" s="4" t="s">
+      <c r="G116" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H116" s="3" t="s">
-        <v>7</v>
+      <c r="H116" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>7</v>
@@ -7450,30 +7489,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="3" t="s">
+    <row r="117" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="7" t="s">
         <v>547</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="B117" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="C117" s="7" t="s">
         <v>548</v>
       </c>
-      <c r="D117" s="3" t="s">
+      <c r="D117" s="7" t="s">
         <v>549</v>
       </c>
-      <c r="E117" s="3" t="s">
+      <c r="E117" s="7" t="s">
         <v>550</v>
       </c>
-      <c r="F117" s="3" t="s">
+      <c r="F117" s="7" t="s">
         <v>551</v>
       </c>
-      <c r="G117" s="4" t="s">
+      <c r="G117" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H117" s="3" t="s">
-        <v>7</v>
+      <c r="H117" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>7</v>
@@ -7488,30 +7527,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="3" t="s">
+    <row r="118" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="7" t="s">
         <v>552</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="B118" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="C118" s="3" t="s">
+      <c r="C118" s="7" t="s">
         <v>553</v>
       </c>
-      <c r="D118" s="3" t="s">
+      <c r="D118" s="7" t="s">
         <v>554</v>
       </c>
-      <c r="E118" s="3" t="s">
+      <c r="E118" s="7" t="s">
         <v>555</v>
       </c>
-      <c r="F118" s="3" t="s">
+      <c r="F118" s="7" t="s">
         <v>556</v>
       </c>
-      <c r="G118" s="5" t="s">
+      <c r="G118" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H118" s="3" t="s">
-        <v>7</v>
+      <c r="H118" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>7</v>
@@ -7526,30 +7565,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="3" t="s">
+    <row r="119" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="7" t="s">
         <v>557</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="B119" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="C119" s="7" t="s">
         <v>558</v>
       </c>
-      <c r="D119" s="3" t="s">
+      <c r="D119" s="7" t="s">
         <v>559</v>
       </c>
-      <c r="E119" s="3" t="s">
+      <c r="E119" s="7" t="s">
         <v>560</v>
       </c>
-      <c r="F119" s="3" t="s">
+      <c r="F119" s="7" t="s">
         <v>561</v>
       </c>
-      <c r="G119" s="5" t="s">
+      <c r="G119" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H119" s="3" t="s">
-        <v>7</v>
+      <c r="H119" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>7</v>
@@ -7564,30 +7603,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="3" t="s">
+    <row r="120" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="7" t="s">
         <v>562</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="B120" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="C120" s="3" t="s">
+      <c r="C120" s="7" t="s">
         <v>563</v>
       </c>
-      <c r="D120" s="3" t="s">
+      <c r="D120" s="7" t="s">
         <v>564</v>
       </c>
-      <c r="E120" s="3" t="s">
+      <c r="E120" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="F120" s="3" t="s">
+      <c r="F120" s="7" t="s">
         <v>566</v>
       </c>
-      <c r="G120" s="5" t="s">
+      <c r="G120" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H120" s="3" t="s">
-        <v>7</v>
+      <c r="H120" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>7</v>
@@ -7602,30 +7641,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="3" t="s">
+    <row r="121" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="7" t="s">
         <v>567</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="B121" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="C121" s="7" t="s">
         <v>568</v>
       </c>
-      <c r="D121" s="3" t="s">
+      <c r="D121" s="7" t="s">
         <v>569</v>
       </c>
-      <c r="E121" s="3" t="s">
+      <c r="E121" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="F121" s="3" t="s">
+      <c r="F121" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="G121" s="6" t="s">
+      <c r="G121" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="H121" s="3" t="s">
-        <v>7</v>
+      <c r="H121" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>7</v>
@@ -7640,30 +7679,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="122" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="3" t="s">
+    <row r="122" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="7" t="s">
         <v>572</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="B122" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="C122" s="7" t="s">
         <v>573</v>
       </c>
-      <c r="D122" s="3" t="s">
+      <c r="D122" s="7" t="s">
         <v>574</v>
       </c>
-      <c r="E122" s="3" t="s">
+      <c r="E122" s="7" t="s">
         <v>575</v>
       </c>
-      <c r="F122" s="3" t="s">
+      <c r="F122" s="7" t="s">
         <v>576</v>
       </c>
-      <c r="G122" s="5" t="s">
+      <c r="G122" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H122" s="3" t="s">
-        <v>7</v>
+      <c r="H122" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>7</v>
@@ -7678,30 +7717,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="123" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="3" t="s">
+    <row r="123" spans="1:12" s="3" customFormat="1" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="7" t="s">
         <v>577</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="C123" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="D123" s="3" t="s">
+      <c r="D123" s="7" t="s">
         <v>579</v>
       </c>
-      <c r="E123" s="3" t="s">
+      <c r="E123" s="7" t="s">
         <v>580</v>
       </c>
-      <c r="F123" s="3" t="s">
+      <c r="F123" s="7" t="s">
         <v>581</v>
       </c>
-      <c r="G123" s="6" t="s">
+      <c r="G123" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="H123" s="3" t="s">
-        <v>7</v>
+      <c r="H123" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>7</v>
@@ -7716,30 +7755,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="124" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="3" t="s">
+    <row r="124" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="7" t="s">
         <v>582</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="B124" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="C124" s="7" t="s">
         <v>583</v>
       </c>
-      <c r="D124" s="3" t="s">
+      <c r="D124" s="7" t="s">
         <v>584</v>
       </c>
-      <c r="E124" s="3" t="s">
+      <c r="E124" s="7" t="s">
         <v>585</v>
       </c>
-      <c r="F124" s="3" t="s">
+      <c r="F124" s="7" t="s">
         <v>586</v>
       </c>
-      <c r="G124" s="6" t="s">
+      <c r="G124" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="H124" s="3" t="s">
-        <v>7</v>
+      <c r="H124" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>7</v>
@@ -7754,30 +7793,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="125" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="3" t="s">
+    <row r="125" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="7" t="s">
         <v>587</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B125" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="C125" s="3" t="s">
+      <c r="C125" s="7" t="s">
         <v>588</v>
       </c>
-      <c r="D125" s="3" t="s">
+      <c r="D125" s="7" t="s">
         <v>589</v>
       </c>
-      <c r="E125" s="3" t="s">
+      <c r="E125" s="7" t="s">
         <v>590</v>
       </c>
-      <c r="F125" s="3" t="s">
+      <c r="F125" s="7" t="s">
         <v>591</v>
       </c>
-      <c r="G125" s="4" t="s">
+      <c r="G125" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H125" s="3" t="s">
-        <v>7</v>
+      <c r="H125" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>7</v>
@@ -7792,30 +7831,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="126" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="3" t="s">
+    <row r="126" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="7" t="s">
         <v>592</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="B126" s="7" t="s">
         <v>593</v>
       </c>
-      <c r="C126" s="3" t="s">
+      <c r="C126" s="7" t="s">
         <v>594</v>
       </c>
-      <c r="D126" s="3" t="s">
+      <c r="D126" s="7" t="s">
         <v>595</v>
       </c>
-      <c r="E126" s="3" t="s">
+      <c r="E126" s="7" t="s">
         <v>596</v>
       </c>
-      <c r="F126" s="3" t="s">
+      <c r="F126" s="7" t="s">
         <v>597</v>
       </c>
-      <c r="G126" s="4" t="s">
+      <c r="G126" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H126" s="3" t="s">
-        <v>7</v>
+      <c r="H126" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>7</v>
@@ -7830,30 +7869,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="3" t="s">
+    <row r="127" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="7" t="s">
         <v>598</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="B127" s="7" t="s">
         <v>593</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="C127" s="7" t="s">
         <v>594</v>
       </c>
-      <c r="D127" s="3" t="s">
+      <c r="D127" s="7" t="s">
         <v>599</v>
       </c>
-      <c r="E127" s="3" t="s">
+      <c r="E127" s="7" t="s">
         <v>600</v>
       </c>
-      <c r="F127" s="3" t="s">
+      <c r="F127" s="7" t="s">
         <v>601</v>
       </c>
-      <c r="G127" s="4" t="s">
+      <c r="G127" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H127" s="3" t="s">
-        <v>7</v>
+      <c r="H127" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>7</v>
@@ -7868,30 +7907,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="128" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="3" t="s">
+    <row r="128" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="7" t="s">
         <v>602</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="B128" s="7" t="s">
         <v>593</v>
       </c>
-      <c r="C128" s="3" t="s">
+      <c r="C128" s="7" t="s">
         <v>603</v>
       </c>
-      <c r="D128" s="3" t="s">
+      <c r="D128" s="7" t="s">
         <v>604</v>
       </c>
-      <c r="E128" s="3" t="s">
+      <c r="E128" s="7" t="s">
         <v>605</v>
       </c>
-      <c r="F128" s="3" t="s">
+      <c r="F128" s="7" t="s">
         <v>606</v>
       </c>
-      <c r="G128" s="5" t="s">
+      <c r="G128" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H128" s="3" t="s">
-        <v>7</v>
+      <c r="H128" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>7</v>
@@ -7906,30 +7945,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="3" t="s">
+    <row r="129" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="7" t="s">
         <v>607</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B129" s="7" t="s">
         <v>593</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="C129" s="7" t="s">
         <v>608</v>
       </c>
-      <c r="D129" s="3" t="s">
+      <c r="D129" s="7" t="s">
         <v>609</v>
       </c>
-      <c r="E129" s="3" t="s">
+      <c r="E129" s="7" t="s">
         <v>610</v>
       </c>
-      <c r="F129" s="3" t="s">
+      <c r="F129" s="7" t="s">
         <v>611</v>
       </c>
-      <c r="G129" s="6" t="s">
+      <c r="G129" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="H129" s="3" t="s">
-        <v>7</v>
+      <c r="H129" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>7</v>
@@ -7945,28 +7984,28 @@
       </c>
     </row>
     <row r="130" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="3" t="s">
+      <c r="A130" s="7" t="s">
         <v>612</v>
       </c>
-      <c r="B130" s="3" t="s">
+      <c r="B130" s="7" t="s">
         <v>613</v>
       </c>
-      <c r="C130" s="3" t="s">
+      <c r="C130" s="7" t="s">
         <v>614</v>
       </c>
-      <c r="D130" s="3" t="s">
+      <c r="D130" s="7" t="s">
         <v>615</v>
       </c>
-      <c r="E130" s="3" t="s">
+      <c r="E130" s="7" t="s">
         <v>616</v>
       </c>
-      <c r="F130" s="3" t="s">
+      <c r="F130" s="7" t="s">
         <v>617</v>
       </c>
-      <c r="G130" s="4" t="s">
+      <c r="G130" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H130" s="3" t="s">
+      <c r="H130" s="7" t="s">
         <v>7</v>
       </c>
       <c r="I130" s="3" t="s">
@@ -7982,29 +8021,29 @@
         <v>7</v>
       </c>
     </row>
-    <row r="131" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="3" t="s">
+    <row r="131" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A131" s="7" t="s">
         <v>618</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B131" s="7" t="s">
         <v>613</v>
       </c>
-      <c r="C131" s="3" t="s">
+      <c r="C131" s="7" t="s">
         <v>614</v>
       </c>
-      <c r="D131" s="3" t="s">
+      <c r="D131" s="7" t="s">
         <v>619</v>
       </c>
-      <c r="E131" s="3" t="s">
+      <c r="E131" s="7" t="s">
         <v>620</v>
       </c>
-      <c r="F131" s="3" t="s">
+      <c r="F131" s="7" t="s">
         <v>621</v>
       </c>
-      <c r="G131" s="4" t="s">
+      <c r="G131" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H131" s="3" t="s">
+      <c r="H131" s="7" t="s">
         <v>7</v>
       </c>
       <c r="I131" s="3" t="s">
@@ -8020,30 +8059,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="3" t="s">
+    <row r="132" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="7" t="s">
         <v>622</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="B132" s="7" t="s">
         <v>613</v>
       </c>
-      <c r="C132" s="3" t="s">
+      <c r="C132" s="7" t="s">
         <v>623</v>
       </c>
-      <c r="D132" s="3" t="s">
+      <c r="D132" s="7" t="s">
         <v>624</v>
       </c>
-      <c r="E132" s="3" t="s">
+      <c r="E132" s="7" t="s">
         <v>625</v>
       </c>
-      <c r="F132" s="3" t="s">
+      <c r="F132" s="7" t="s">
         <v>626</v>
       </c>
-      <c r="G132" s="5" t="s">
+      <c r="G132" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H132" s="3" t="s">
-        <v>7</v>
+      <c r="H132" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I132" s="3" t="s">
         <v>7</v>
@@ -8058,30 +8097,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="133" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="3" t="s">
+    <row r="133" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="7" t="s">
         <v>627</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B133" s="7" t="s">
         <v>613</v>
       </c>
-      <c r="C133" s="3" t="s">
+      <c r="C133" s="7" t="s">
         <v>623</v>
       </c>
-      <c r="D133" s="3" t="s">
+      <c r="D133" s="7" t="s">
         <v>628</v>
       </c>
-      <c r="E133" s="3" t="s">
+      <c r="E133" s="7" t="s">
         <v>629</v>
       </c>
-      <c r="F133" s="3" t="s">
+      <c r="F133" s="7" t="s">
         <v>630</v>
       </c>
-      <c r="G133" s="5" t="s">
+      <c r="G133" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H133" s="3" t="s">
-        <v>7</v>
+      <c r="H133" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>7</v>
@@ -8096,30 +8135,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="134" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="3" t="s">
+    <row r="134" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="7" t="s">
         <v>631</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="B134" s="7" t="s">
         <v>632</v>
       </c>
-      <c r="C134" s="3" t="s">
+      <c r="C134" s="7" t="s">
         <v>633</v>
       </c>
-      <c r="D134" s="3" t="s">
+      <c r="D134" s="7" t="s">
         <v>634</v>
       </c>
-      <c r="E134" s="3" t="s">
+      <c r="E134" s="7" t="s">
         <v>635</v>
       </c>
-      <c r="F134" s="3" t="s">
+      <c r="F134" s="7" t="s">
         <v>636</v>
       </c>
-      <c r="G134" s="6" t="s">
+      <c r="G134" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="H134" s="3" t="s">
-        <v>7</v>
+      <c r="H134" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I134" s="3" t="s">
         <v>7</v>
@@ -8134,7 +8173,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="135" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>637</v>
       </c>
@@ -8249,28 +8288,28 @@
       </c>
     </row>
     <row r="138" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="3" t="s">
+      <c r="A138" s="7" t="s">
         <v>650</v>
       </c>
-      <c r="B138" s="3" t="s">
+      <c r="B138" s="7" t="s">
         <v>632</v>
       </c>
-      <c r="C138" s="3" t="s">
+      <c r="C138" s="7" t="s">
         <v>651</v>
       </c>
-      <c r="D138" s="3" t="s">
+      <c r="D138" s="7" t="s">
         <v>652</v>
       </c>
-      <c r="E138" s="3" t="s">
+      <c r="E138" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="F138" s="3" t="s">
+      <c r="F138" s="7" t="s">
         <v>654</v>
       </c>
-      <c r="G138" s="6" t="s">
+      <c r="G138" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="H138" s="3" t="s">
+      <c r="H138" s="7" t="s">
         <v>7</v>
       </c>
       <c r="I138" s="3" t="s">
@@ -8286,30 +8325,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="139" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="3" t="s">
+    <row r="139" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="7" t="s">
         <v>655</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="B139" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="C139" s="3" t="s">
+      <c r="C139" s="7" t="s">
         <v>656</v>
       </c>
-      <c r="D139" s="3" t="s">
+      <c r="D139" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="E139" s="3" t="s">
+      <c r="E139" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="F139" s="3" t="s">
+      <c r="F139" s="7" t="s">
         <v>659</v>
       </c>
-      <c r="G139" s="5" t="s">
+      <c r="G139" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H139" s="3" t="s">
-        <v>7</v>
+      <c r="H139" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I139" s="3" t="s">
         <v>7</v>
@@ -8324,29 +8363,29 @@
         <v>7</v>
       </c>
     </row>
-    <row r="140" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="3" t="s">
+    <row r="140" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A140" s="7" t="s">
         <v>660</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="B140" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="C140" s="3" t="s">
+      <c r="C140" s="7" t="s">
         <v>661</v>
       </c>
-      <c r="D140" s="3" t="s">
+      <c r="D140" s="7" t="s">
         <v>662</v>
       </c>
-      <c r="E140" s="3" t="s">
+      <c r="E140" s="7" t="s">
         <v>663</v>
       </c>
-      <c r="F140" s="3" t="s">
+      <c r="F140" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="G140" s="5" t="s">
+      <c r="G140" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H140" s="3" t="s">
+      <c r="H140" s="7" t="s">
         <v>7</v>
       </c>
       <c r="I140" s="3" t="s">
@@ -8362,30 +8401,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="141" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="3" t="s">
+    <row r="141" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="7" t="s">
         <v>665</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="B141" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="C141" s="3" t="s">
+      <c r="C141" s="7" t="s">
         <v>666</v>
       </c>
-      <c r="D141" s="3" t="s">
+      <c r="D141" s="7" t="s">
         <v>667</v>
       </c>
-      <c r="E141" s="3" t="s">
+      <c r="E141" s="7" t="s">
         <v>668</v>
       </c>
-      <c r="F141" s="3" t="s">
+      <c r="F141" s="7" t="s">
         <v>669</v>
       </c>
-      <c r="G141" s="6" t="s">
+      <c r="G141" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="H141" s="3" t="s">
-        <v>7</v>
+      <c r="H141" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I141" s="3" t="s">
         <v>7</v>
@@ -8400,30 +8439,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="142" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="3" t="s">
+    <row r="142" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="7" t="s">
         <v>670</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="B142" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="C142" s="3" t="s">
+      <c r="C142" s="7" t="s">
         <v>671</v>
       </c>
-      <c r="D142" s="3" t="s">
+      <c r="D142" s="7" t="s">
         <v>667</v>
       </c>
-      <c r="E142" s="3" t="s">
+      <c r="E142" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="F142" s="3" t="s">
+      <c r="F142" s="7" t="s">
         <v>673</v>
       </c>
-      <c r="G142" s="6" t="s">
+      <c r="G142" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="H142" s="3" t="s">
-        <v>7</v>
+      <c r="H142" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I142" s="3" t="s">
         <v>7</v>
@@ -8438,30 +8477,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="143" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="3" t="s">
+    <row r="143" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="7" t="s">
         <v>674</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="B143" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="C143" s="3" t="s">
+      <c r="C143" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="D143" s="3" t="s">
+      <c r="D143" s="7" t="s">
         <v>667</v>
       </c>
-      <c r="E143" s="3" t="s">
+      <c r="E143" s="7" t="s">
         <v>676</v>
       </c>
-      <c r="F143" s="3" t="s">
+      <c r="F143" s="7" t="s">
         <v>673</v>
       </c>
-      <c r="G143" s="6" t="s">
+      <c r="G143" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="H143" s="3" t="s">
-        <v>7</v>
+      <c r="H143" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I143" s="3" t="s">
         <v>7</v>
@@ -8628,30 +8667,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="148" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="3" t="s">
+    <row r="148" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="7" t="s">
         <v>697</v>
       </c>
-      <c r="B148" s="3" t="s">
+      <c r="B148" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="C148" s="3" t="s">
+      <c r="C148" s="7" t="s">
         <v>698</v>
       </c>
-      <c r="D148" s="3" t="s">
+      <c r="D148" s="7" t="s">
         <v>699</v>
       </c>
-      <c r="E148" s="3" t="s">
+      <c r="E148" s="7" t="s">
         <v>700</v>
       </c>
-      <c r="F148" s="3" t="s">
+      <c r="F148" s="7" t="s">
         <v>701</v>
       </c>
-      <c r="G148" s="6" t="s">
+      <c r="G148" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="H148" s="3" t="s">
-        <v>7</v>
+      <c r="H148" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I148" s="3" t="s">
         <v>7</v>
@@ -8666,7 +8705,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="149" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>702</v>
       </c>
@@ -8704,7 +8743,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="150" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>708</v>
       </c>
@@ -8742,7 +8781,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="151" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
         <v>713</v>
       </c>
@@ -8780,7 +8819,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="152" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>718</v>
       </c>
@@ -8818,7 +8857,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="153" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
         <v>722</v>
       </c>
@@ -8856,7 +8895,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="154" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
         <v>727</v>
       </c>
@@ -8894,30 +8933,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="155" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="3" t="s">
+    <row r="155" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="7" t="s">
         <v>732</v>
       </c>
-      <c r="B155" s="3" t="s">
+      <c r="B155" s="7" t="s">
         <v>733</v>
       </c>
-      <c r="C155" s="3" t="s">
+      <c r="C155" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="D155" s="3" t="s">
+      <c r="D155" s="7" t="s">
         <v>734</v>
       </c>
-      <c r="E155" s="3" t="s">
+      <c r="E155" s="7" t="s">
         <v>735</v>
       </c>
-      <c r="F155" s="3" t="s">
+      <c r="F155" s="7" t="s">
         <v>736</v>
       </c>
-      <c r="G155" s="5" t="s">
+      <c r="G155" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H155" s="3" t="s">
-        <v>7</v>
+      <c r="H155" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I155" s="3" t="s">
         <v>7</v>
@@ -8932,30 +8971,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="3" t="s">
+    <row r="156" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="7" t="s">
         <v>737</v>
       </c>
-      <c r="B156" s="3" t="s">
+      <c r="B156" s="7" t="s">
         <v>733</v>
       </c>
-      <c r="C156" s="3" t="s">
+      <c r="C156" s="7" t="s">
         <v>738</v>
       </c>
-      <c r="D156" s="3" t="s">
+      <c r="D156" s="7" t="s">
         <v>739</v>
       </c>
-      <c r="E156" s="3" t="s">
+      <c r="E156" s="7" t="s">
         <v>740</v>
       </c>
-      <c r="F156" s="3" t="s">
+      <c r="F156" s="7" t="s">
         <v>741</v>
       </c>
-      <c r="G156" s="4" t="s">
+      <c r="G156" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H156" s="3" t="s">
-        <v>7</v>
+      <c r="H156" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I156" s="3" t="s">
         <v>7</v>
@@ -8970,30 +9009,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="157" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="3" t="s">
+    <row r="157" spans="1:12" s="3" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="7" t="s">
         <v>742</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="B157" s="7" t="s">
         <v>733</v>
       </c>
-      <c r="C157" s="3" t="s">
+      <c r="C157" s="7" t="s">
         <v>743</v>
       </c>
-      <c r="D157" s="3" t="s">
+      <c r="D157" s="7" t="s">
         <v>744</v>
       </c>
-      <c r="E157" s="3" t="s">
+      <c r="E157" s="7" t="s">
         <v>745</v>
       </c>
-      <c r="F157" s="3" t="s">
+      <c r="F157" s="7" t="s">
         <v>746</v>
       </c>
-      <c r="G157" s="5" t="s">
+      <c r="G157" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H157" s="3" t="s">
-        <v>7</v>
+      <c r="H157" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I157" s="3" t="s">
         <v>7</v>
@@ -9008,30 +9047,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="158" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="3" t="s">
+    <row r="158" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="7" t="s">
         <v>747</v>
       </c>
-      <c r="B158" s="3" t="s">
+      <c r="B158" s="7" t="s">
         <v>748</v>
       </c>
-      <c r="C158" s="3" t="s">
+      <c r="C158" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="D158" s="3" t="s">
+      <c r="D158" s="7" t="s">
         <v>750</v>
       </c>
-      <c r="E158" s="3" t="s">
+      <c r="E158" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="F158" s="3" t="s">
+      <c r="F158" s="7" t="s">
         <v>752</v>
       </c>
-      <c r="G158" s="5" t="s">
+      <c r="G158" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H158" s="3" t="s">
-        <v>7</v>
+      <c r="H158" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I158" s="3" t="s">
         <v>7</v>
@@ -9046,30 +9085,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="159" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="3" t="s">
+    <row r="159" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="B159" s="3" t="s">
+      <c r="B159" s="7" t="s">
         <v>748</v>
       </c>
-      <c r="C159" s="3" t="s">
+      <c r="C159" s="7" t="s">
         <v>754</v>
       </c>
-      <c r="D159" s="3" t="s">
+      <c r="D159" s="7" t="s">
         <v>755</v>
       </c>
-      <c r="E159" s="3" t="s">
+      <c r="E159" s="7" t="s">
         <v>756</v>
       </c>
-      <c r="F159" s="3" t="s">
+      <c r="F159" s="7" t="s">
         <v>757</v>
       </c>
-      <c r="G159" s="6" t="s">
+      <c r="G159" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="H159" s="3" t="s">
-        <v>7</v>
+      <c r="H159" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I159" s="3" t="s">
         <v>7</v>
@@ -9084,30 +9123,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="160" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="3" t="s">
+    <row r="160" spans="1:12" s="3" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="7" t="s">
         <v>758</v>
       </c>
-      <c r="B160" s="3" t="s">
+      <c r="B160" s="7" t="s">
         <v>759</v>
       </c>
-      <c r="C160" s="3" t="s">
+      <c r="C160" s="7" t="s">
         <v>760</v>
       </c>
-      <c r="D160" s="3" t="s">
+      <c r="D160" s="7" t="s">
         <v>761</v>
       </c>
-      <c r="E160" s="3" t="s">
+      <c r="E160" s="7" t="s">
         <v>762</v>
       </c>
-      <c r="F160" s="3" t="s">
+      <c r="F160" s="7" t="s">
         <v>763</v>
       </c>
-      <c r="G160" s="5" t="s">
+      <c r="G160" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H160" s="3" t="s">
-        <v>7</v>
+      <c r="H160" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I160" s="3" t="s">
         <v>7</v>
@@ -9122,30 +9161,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="161" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="3" t="s">
+    <row r="161" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="7" t="s">
         <v>764</v>
       </c>
-      <c r="B161" s="3" t="s">
+      <c r="B161" s="7" t="s">
         <v>759</v>
       </c>
-      <c r="C161" s="3" t="s">
+      <c r="C161" s="7" t="s">
         <v>765</v>
       </c>
-      <c r="D161" s="3" t="s">
+      <c r="D161" s="7" t="s">
         <v>766</v>
       </c>
-      <c r="E161" s="3" t="s">
+      <c r="E161" s="7" t="s">
         <v>767</v>
       </c>
-      <c r="F161" s="3" t="s">
+      <c r="F161" s="7" t="s">
         <v>768</v>
       </c>
-      <c r="G161" s="5" t="s">
+      <c r="G161" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H161" s="3" t="s">
-        <v>7</v>
+      <c r="H161" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I161" s="3" t="s">
         <v>7</v>
@@ -9160,30 +9199,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="3" t="s">
+    <row r="162" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="7" t="s">
         <v>769</v>
       </c>
-      <c r="B162" s="3" t="s">
+      <c r="B162" s="7" t="s">
         <v>759</v>
       </c>
-      <c r="C162" s="3" t="s">
+      <c r="C162" s="7" t="s">
         <v>770</v>
       </c>
-      <c r="D162" s="3" t="s">
+      <c r="D162" s="7" t="s">
         <v>771</v>
       </c>
-      <c r="E162" s="3" t="s">
+      <c r="E162" s="7" t="s">
         <v>772</v>
       </c>
-      <c r="F162" s="3" t="s">
+      <c r="F162" s="7" t="s">
         <v>773</v>
       </c>
-      <c r="G162" s="6" t="s">
+      <c r="G162" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="H162" s="3" t="s">
-        <v>7</v>
+      <c r="H162" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I162" s="3" t="s">
         <v>7</v>
@@ -9198,30 +9237,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="163" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="3" t="s">
+    <row r="163" spans="1:12" s="3" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="7" t="s">
         <v>774</v>
       </c>
-      <c r="B163" s="3" t="s">
+      <c r="B163" s="7" t="s">
         <v>775</v>
       </c>
-      <c r="C163" s="3" t="s">
+      <c r="C163" s="7" t="s">
         <v>593</v>
       </c>
-      <c r="D163" s="3" t="s">
+      <c r="D163" s="7" t="s">
         <v>776</v>
       </c>
-      <c r="E163" s="3" t="s">
+      <c r="E163" s="7" t="s">
         <v>777</v>
       </c>
-      <c r="F163" s="3" t="s">
+      <c r="F163" s="7" t="s">
         <v>778</v>
       </c>
-      <c r="G163" s="4" t="s">
+      <c r="G163" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H163" s="3" t="s">
-        <v>7</v>
+      <c r="H163" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I163" s="3" t="s">
         <v>7</v>
@@ -9236,30 +9275,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="3" t="s">
+    <row r="164" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="7" t="s">
         <v>779</v>
       </c>
-      <c r="B164" s="3" t="s">
+      <c r="B164" s="7" t="s">
         <v>775</v>
       </c>
-      <c r="C164" s="3" t="s">
+      <c r="C164" s="7" t="s">
         <v>780</v>
       </c>
-      <c r="D164" s="3" t="s">
+      <c r="D164" s="7" t="s">
         <v>781</v>
       </c>
-      <c r="E164" s="3" t="s">
+      <c r="E164" s="7" t="s">
         <v>782</v>
       </c>
-      <c r="F164" s="3" t="s">
+      <c r="F164" s="7" t="s">
         <v>783</v>
       </c>
-      <c r="G164" s="4" t="s">
+      <c r="G164" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H164" s="3" t="s">
-        <v>7</v>
+      <c r="H164" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I164" s="3" t="s">
         <v>7</v>
@@ -9274,30 +9313,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="165" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="3" t="s">
+    <row r="165" spans="1:12" s="3" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="7" t="s">
         <v>784</v>
       </c>
-      <c r="B165" s="3" t="s">
+      <c r="B165" s="7" t="s">
         <v>775</v>
       </c>
-      <c r="C165" s="3" t="s">
+      <c r="C165" s="7" t="s">
         <v>785</v>
       </c>
-      <c r="D165" s="3" t="s">
+      <c r="D165" s="7" t="s">
         <v>786</v>
       </c>
-      <c r="E165" s="3" t="s">
+      <c r="E165" s="7" t="s">
         <v>787</v>
       </c>
-      <c r="F165" s="3" t="s">
+      <c r="F165" s="7" t="s">
         <v>788</v>
       </c>
-      <c r="G165" s="4" t="s">
+      <c r="G165" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H165" s="3" t="s">
-        <v>7</v>
+      <c r="H165" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I165" s="3" t="s">
         <v>7</v>
@@ -9312,30 +9351,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="166" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="3" t="s">
+    <row r="166" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="7" t="s">
         <v>789</v>
       </c>
-      <c r="B166" s="3" t="s">
+      <c r="B166" s="7" t="s">
         <v>775</v>
       </c>
-      <c r="C166" s="3" t="s">
+      <c r="C166" s="7" t="s">
         <v>790</v>
       </c>
-      <c r="D166" s="3" t="s">
+      <c r="D166" s="7" t="s">
         <v>791</v>
       </c>
-      <c r="E166" s="3" t="s">
+      <c r="E166" s="7" t="s">
         <v>792</v>
       </c>
-      <c r="F166" s="3" t="s">
+      <c r="F166" s="7" t="s">
         <v>793</v>
       </c>
-      <c r="G166" s="4" t="s">
+      <c r="G166" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H166" s="3" t="s">
-        <v>7</v>
+      <c r="H166" s="7" t="s">
+        <v>794</v>
       </c>
       <c r="I166" s="3" t="s">
         <v>7</v>
@@ -9351,12 +9390,17 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="H1:H166" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="0">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid status" error="Pick one of: Pass, Fail, Blocked, Skipped, N/A" sqref="H2:H166">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid status" error="Pick one of: Pass, Fail, Blocked, Skipped, N/A" sqref="H2:H166" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Pass,Fail,Blocked,Skipped,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>